--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F65096-9AFE-4291-BCD6-B2F5444B1051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{402C1287-1372-4E95-AFF6-A0271692EC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="152">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -208,6 +208,279 @@
   </si>
   <si>
     <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Marcus Sasser</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Javonte Green</t>
+  </si>
+  <si>
+    <t>Wendell Moore</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Adou Thiero</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Obi Toppin</t>
+  </si>
+  <si>
+    <t>Isaac Okoro</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Guershchon Yabusele</t>
+  </si>
+  <si>
+    <t>Jaden Ivey</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Quentin Grimes</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Kelly Oubre</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Larry Nance</t>
+  </si>
+  <si>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Luke Kornet</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>Jaylen Wells</t>
+  </si>
+  <si>
+    <t>Javon Small</t>
+  </si>
+  <si>
+    <t>Jahmai Mashack</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>D'Angelo Russell</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Cody Williams</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Kyle Filipowski</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Brice Sensabaugh</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Brandon Williams</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Seth Curry</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Gary Harris</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Robert Williams</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Jakob Poeltl</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>Jordan Miller</t>
   </si>
 </sst>
 </file>
@@ -311,10 +584,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,15 +899,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -757,7 +1030,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="11">
+      <c r="A2" s="9">
         <v>46105</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -777,7 +1050,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>46105</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -797,7 +1070,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="11">
+      <c r="A4" s="9">
         <v>46105</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -817,7 +1090,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>46105</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -834,7 +1107,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="11">
+      <c r="A6" s="9">
         <v>46105</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -851,7 +1124,7 @@
       <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>46105</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -868,7 +1141,7 @@
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="11">
+      <c r="A8" s="9">
         <v>46105</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -885,7 +1158,7 @@
       <c r="G8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>46105</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -902,7 +1175,7 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>46105</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -919,7 +1192,7 @@
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>46105</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -936,7 +1209,7 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" s="11">
+      <c r="A12" s="9">
         <v>46105</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -953,7 +1226,7 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>46105</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -970,7 +1243,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" s="11">
+      <c r="A14" s="9">
         <v>46105</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -987,7 +1260,7 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>46105</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -1004,7 +1277,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" s="11">
+      <c r="A16" s="9">
         <v>46105</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1021,7 +1294,7 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>46105</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -1038,7 +1311,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="11">
+      <c r="A18" s="9">
         <v>46105</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -1055,7 +1328,7 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>46105</v>
       </c>
       <c r="B19" s="7" t="s">
@@ -1072,7 +1345,7 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="11">
+      <c r="A20" s="9">
         <v>46105</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -1089,7 +1362,7 @@
       <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>46105</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -1106,7 +1379,7 @@
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="11">
+      <c r="A22" s="9">
         <v>46105</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -1123,7 +1396,7 @@
       <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>46105</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -1140,7 +1413,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="11">
+      <c r="A24" s="9">
         <v>46105</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -1157,7 +1430,7 @@
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="12">
+      <c r="A25" s="10">
         <v>46105</v>
       </c>
       <c r="B25" s="7" t="s">
@@ -1174,7 +1447,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="11">
+      <c r="A26" s="9">
         <v>46105</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -1191,7 +1464,7 @@
       <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="12">
+      <c r="A27" s="10">
         <v>46105</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -1208,7 +1481,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="11">
+      <c r="A28" s="9">
         <v>46105</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -1225,685 +1498,1293 @@
       <c r="G28" s="6"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="A29" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+      <c r="A30" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
+      <c r="A31" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
+      <c r="A32" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="A33" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
+      <c r="A34" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="A35" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="A36" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
+      <c r="A37" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
+      <c r="A38" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
+      <c r="A39" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="A40" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="A41" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="A42" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="A43" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
+      <c r="A44" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="A45" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="A46" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
+      <c r="A47" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
+      <c r="A48" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="A49" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
+      <c r="A50" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
+      <c r="A51" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
+      <c r="A52" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
+      <c r="A53" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+      <c r="A54" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
+      <c r="A55" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
+      <c r="A56" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="A57" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
+      <c r="A58" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
+      <c r="A59" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="A60" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
+      <c r="A61" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="A62" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
+      <c r="A63" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="A64" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
+      <c r="A65" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="A66" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
+      <c r="A67" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
+      <c r="A68" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
+      <c r="A69" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
+      <c r="A70" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
+      <c r="A71" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
+      <c r="A72" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
+      <c r="A73" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
+      <c r="A74" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
+      <c r="A75" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E75" s="7"/>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="A76" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
+      <c r="A77" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="A78" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
+      <c r="A79" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
+      <c r="A80" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
+      <c r="A81" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
+      <c r="A82" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
+      <c r="A83" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
+      <c r="A84" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
+      <c r="A85" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
+      <c r="A86" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
+      <c r="A87" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
+      <c r="A88" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
+      <c r="A89" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
+      <c r="A90" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
+      <c r="A91" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
+      <c r="A92" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
+      <c r="A93" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
+      <c r="A94" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
+      <c r="A95" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
+      <c r="A96" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
+      <c r="A97" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
+      <c r="A98" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
+      <c r="A99" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
+      <c r="A100" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
+      <c r="A101" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
+      <c r="A102" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
+      <c r="A103" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
+      <c r="A104" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C970569-4916-45F4-822E-5433DCAB1D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F1D34D-A2FC-4B39-B550-07B4DB1D3070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="status_reference" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">injuries_input!$A$1:$G$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">injuries_input!$A$1:$G$200</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="154">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,6 +96,15 @@
     <t>Quick rules</t>
   </si>
   <si>
+    <t>Out / Doubtful -&gt; remove</t>
+  </si>
+  <si>
+    <t>Questionable / Probable -&gt; tag</t>
+  </si>
+  <si>
+    <t>Leave blank to ignore player</t>
+  </si>
+  <si>
     <t>Nique Clifford</t>
   </si>
   <si>
@@ -114,6 +123,12 @@
     <t>Precious Achiuwa</t>
   </si>
   <si>
+    <t>Daeqwon Plowden</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
+  </si>
+  <si>
     <t>CHA</t>
   </si>
   <si>
@@ -126,6 +141,9 @@
     <t>NOP</t>
   </si>
   <si>
+    <t>Kevin McCuller</t>
+  </si>
+  <si>
     <t>NYK</t>
   </si>
   <si>
@@ -150,6 +168,54 @@
     <t>Franz Wagner</t>
   </si>
   <si>
+    <t>Tyrese Proctor</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Craig Porter</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Royce O'Neale</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Grayson Allen</t>
+  </si>
+  <si>
+    <t>Dillon Brooks</t>
+  </si>
+  <si>
+    <t>Amir Coffey</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
     <t>DET</t>
   </si>
   <si>
@@ -162,16 +228,265 @@
     <t>Isaiah Stewart</t>
   </si>
   <si>
+    <t>Javonte Green</t>
+  </si>
+  <si>
+    <t>Wendell Moore</t>
+  </si>
+  <si>
+    <t>Rui Hachimura</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Adou Thiero</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Obi Toppin</t>
+  </si>
+  <si>
+    <t>Isaac Okoro</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Guershchon Yabusele</t>
+  </si>
+  <si>
+    <t>Jaden Ivey</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Quentin Grimes</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Kelly Oubre</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Larry Nance</t>
+  </si>
+  <si>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Luke Kornet</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>Jaylen Wells</t>
+  </si>
+  <si>
+    <t>Javon Small</t>
+  </si>
+  <si>
+    <t>Jahmai Mashack</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>D'Angelo Russell</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Cody Williams</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Kyle Filipowski</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Brice Sensabaugh</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Brandon Williams</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Seth Curry</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Gary Harris</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Robert Williams</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Jakob Poeltl</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>Jordan Miller</t>
+  </si>
+  <si>
     <t>Trey Murphy III</t>
   </si>
   <si>
     <t>Dejounte Murray</t>
-  </si>
-  <si>
-    <t>Pat Connaughton</t>
-  </si>
-  <si>
-    <t>Isaiah Stevens</t>
   </si>
 </sst>
 </file>
@@ -263,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -276,6 +591,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -589,15 +905,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -681,7 +997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -721,580 +1037,2276 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="A3" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="A5" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="A7" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B10" s="7" t="s">
+        <v>46105</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="D10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="C11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B12" s="7" t="s">
+        <v>46105</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="C12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="D13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="A15" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="A17" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+        <v>46105</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="9">
-        <v>46107</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="A19" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A59" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A60" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A62" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A63" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A64" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A65" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A66" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A67" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A68" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A69" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A70" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A71" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A72" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A73" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A74" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A75" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A76" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A77" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A78" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A79" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A80" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A81" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A82" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A83" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A84" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A85" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A86" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A87" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A88" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A89" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A90" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A91" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A92" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A93" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A94" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A95" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A96" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A97" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A98" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A99" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A100" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A101" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A102" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A103" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A104" s="9">
+        <v>46106</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A105" s="9">
         <v>46107</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="9">
+      <c r="B105" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A106" s="9">
         <v>46107</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
+      <c r="B106" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A107" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A108" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A109" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A110" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A111" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A112" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A113" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A114" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A115" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A116" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A118" s="6"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A120" s="6"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A127" s="7"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="7"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="7"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A130" s="6"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="6"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A131" s="7"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A135" s="7"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A138" s="6"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="6"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A142" s="6"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="6"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="6"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A150" s="6"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G97" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G200" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1303,7 +3315,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D397</xm:sqref>
+          <xm:sqref>D2:D500</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC917F2-3FCC-49B5-9F48-FC4A28F7A4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A0BA91-9673-45F0-AA69-4218EA163E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="88">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Moses Moody</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1618,6 +1621,20 @@
         <v>28</v>
       </c>
       <c r="D50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46108</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A0BA91-9673-45F0-AA69-4218EA163E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6898AFD3-47DC-4188-BFEF-237789A01C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="status_reference" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">injuries_input!$A$1:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">injuries_input!$A$1:$G$53</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="91">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -108,18 +108,6 @@
     <t>Craig Porter</t>
   </si>
   <si>
-    <t>Rui Hachimura</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Adou Thiero</t>
-  </si>
-  <si>
     <t>IND</t>
   </si>
   <si>
@@ -159,33 +147,9 @@
     <t>Jahmai Mashack</t>
   </si>
   <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Alex Sarr</t>
-  </si>
-  <si>
-    <t>Trae Young</t>
-  </si>
-  <si>
     <t>UTA</t>
   </si>
   <si>
-    <t>Kyle Filipowski</t>
-  </si>
-  <si>
     <t>Isaiah Collier</t>
   </si>
   <si>
@@ -195,63 +159,6 @@
     <t>Lauri Markkanen</t>
   </si>
   <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>Caleb Martin</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Danny Wolf</t>
-  </si>
-  <si>
-    <t>Seth Curry</t>
-  </si>
-  <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>Stephen Curry</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Quinten Post</t>
-  </si>
-  <si>
-    <t>Vit Krejci</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Robert Williams</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Chucky Hepburn</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
@@ -282,13 +189,115 @@
     <t>Nick Richards</t>
   </si>
   <si>
-    <t>Nick Smith</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Moses Moody</t>
+    <t>Gary Harris</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Caris LeVert</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Marcus Sasser</t>
+  </si>
+  <si>
+    <t>Jalen Duren</t>
+  </si>
+  <si>
+    <t>Tobias Harris</t>
+  </si>
+  <si>
+    <t>Duncan Robinson</t>
+  </si>
+  <si>
+    <t>Ausar Thompson</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Kelly Oubre Jr.</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>Tidjane Salaun</t>
+  </si>
+  <si>
+    <t>Nique Clifford</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Killian Hayes</t>
+  </si>
+  <si>
+    <t>Keegan Murray</t>
+  </si>
+  <si>
+    <t>Russell Westbrook</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Dillon Brooks</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Amir Coffey</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
   </si>
 </sst>
 </file>
@@ -798,7 +807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -841,10 +850,10 @@
         <v>46108</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>11</v>
@@ -858,10 +867,10 @@
         <v>46108</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>9</v>
@@ -875,10 +884,10 @@
         <v>46108</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>11</v>
@@ -892,10 +901,10 @@
         <v>46108</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>11</v>
@@ -909,10 +918,10 @@
         <v>46108</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>11</v>
@@ -926,10 +935,10 @@
         <v>46108</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
@@ -943,10 +952,10 @@
         <v>46108</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -960,10 +969,10 @@
         <v>46108</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
@@ -1028,7 +1037,7 @@
         <v>46108</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>23</v>
@@ -1045,10 +1054,10 @@
         <v>46108</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>9</v>
@@ -1062,10 +1071,10 @@
         <v>46108</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>9</v>
@@ -1079,10 +1088,10 @@
         <v>46108</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>11</v>
@@ -1096,10 +1105,10 @@
         <v>46108</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -1113,10 +1122,10 @@
         <v>46108</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>12</v>
@@ -1130,10 +1139,10 @@
         <v>46108</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>12</v>
@@ -1144,453 +1153,405 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -1598,48 +1559,132 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G53" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1648,7 +1693,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D385</xm:sqref>
+          <xm:sqref>D2:D353</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6898AFD3-47DC-4188-BFEF-237789A01C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BE1D3A-36A0-408D-97D1-A802572B9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="status_reference" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">injuries_input!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">injuries_input!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="94">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,18 +96,6 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>Craig Porter</t>
-  </si>
-  <si>
     <t>IND</t>
   </si>
   <si>
@@ -117,54 +105,15 @@
     <t>Obi Toppin</t>
   </si>
   <si>
-    <t>Isaac Okoro</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>Anfernee Simons</t>
-  </si>
-  <si>
-    <t>Guershchon Yabusele</t>
-  </si>
-  <si>
     <t>Nikola Vucevic</t>
   </si>
   <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>Ty Jerome</t>
-  </si>
-  <si>
-    <t>MEM</t>
-  </si>
-  <si>
-    <t>Jaylen Wells</t>
-  </si>
-  <si>
-    <t>Jahmai Mashack</t>
-  </si>
-  <si>
-    <t>UTA</t>
-  </si>
-  <si>
-    <t>Isaiah Collier</t>
-  </si>
-  <si>
-    <t>Keyonte George</t>
-  </si>
-  <si>
-    <t>Lauri Markkanen</t>
-  </si>
-  <si>
     <t>LAC</t>
   </si>
   <si>
-    <t>Jordan Miller</t>
-  </si>
-  <si>
     <t>Jaylen Brown</t>
   </si>
   <si>
@@ -174,21 +123,9 @@
     <t>Derrick White</t>
   </si>
   <si>
-    <t>Jaime Jaquez</t>
-  </si>
-  <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
-    <t>Rob Dillingham</t>
-  </si>
-  <si>
-    <t>Nick Richards</t>
-  </si>
-  <si>
     <t>Gary Harris</t>
   </si>
   <si>
@@ -201,103 +138,175 @@
     <t>Bobby Portis</t>
   </si>
   <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
     <t>Giannis Antetokounmpo</t>
   </si>
   <si>
     <t>Kevin Porter Jr.</t>
   </si>
   <si>
-    <t>Caris LeVert</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Marcus Sasser</t>
-  </si>
-  <si>
-    <t>Jalen Duren</t>
-  </si>
-  <si>
-    <t>Tobias Harris</t>
-  </si>
-  <si>
-    <t>Duncan Robinson</t>
-  </si>
-  <si>
-    <t>Ausar Thompson</t>
-  </si>
-  <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
-    <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Kelly Oubre Jr.</t>
-  </si>
-  <si>
-    <t>Johni Broome</t>
-  </si>
-  <si>
     <t>Tidjane Salaun</t>
   </si>
   <si>
-    <t>Nique Clifford</t>
-  </si>
-  <si>
     <t>SAC</t>
   </si>
   <si>
-    <t>Killian Hayes</t>
-  </si>
-  <si>
     <t>Keegan Murray</t>
   </si>
   <si>
     <t>Russell Westbrook</t>
   </si>
   <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Dillon Brooks</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Amir Coffey</t>
-  </si>
-  <si>
-    <t>Haywood Highsmith</t>
-  </si>
-  <si>
-    <t>Mark Williams</t>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>Thanasis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Norman Powell</t>
+  </si>
+  <si>
+    <t>TJ McConnell</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>Isaiah Stevens</t>
+  </si>
+  <si>
+    <t>Josh Minott</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>Leaky Black</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Robert Williams</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Issac</t>
+  </si>
+  <si>
+    <t>Franz Wagner</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Trayce Jackson-Davis</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Immanual Quickley</t>
+  </si>
+  <si>
+    <t>Jayson Tatum</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>Trey Murphy III</t>
+  </si>
+  <si>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>Dejounte Murray</t>
+  </si>
+  <si>
+    <t>Bryce McGowens</t>
+  </si>
+  <si>
+    <t>Kevin McCullar</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Miles McBride</t>
+  </si>
+  <si>
+    <t>Landry Shamet</t>
+  </si>
+  <si>
+    <t>Seth Curry</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Will Richard</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
   </si>
 </sst>
 </file>
@@ -847,177 +856,147 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>24</v>
@@ -1025,309 +1004,285 @@
       <c r="C12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="9">
-        <v>46108</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="9">
-        <v>46108</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="9">
-        <v>46108</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="C28" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B30" s="7" t="s">
+      <c r="C30" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="9">
-        <v>46109</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="C32" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -1335,13 +1290,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -1349,27 +1304,27 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -1377,27 +1332,27 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -1405,13 +1360,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -1419,13 +1374,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -1433,13 +1388,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -1447,13 +1402,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -1461,13 +1416,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -1475,69 +1430,69 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -1545,13 +1500,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -1559,27 +1514,27 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -1587,83 +1542,83 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="D56" t="s">
         <v>14</v>
@@ -1671,20 +1626,20 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="9">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G53" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1693,7 +1648,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D353</xm:sqref>
+          <xm:sqref>D2:D297</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BE1D3A-36A0-408D-97D1-A802572B9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9954A1F1-07E9-4149-89DF-97FDB2672704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,111 +96,27 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>Aaron Nesmith</t>
-  </si>
-  <si>
-    <t>Obi Toppin</t>
-  </si>
-  <si>
     <t>Nikola Vucevic</t>
   </si>
   <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>LAC</t>
-  </si>
-  <si>
     <t>Jaylen Brown</t>
   </si>
   <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
     <t>Derrick White</t>
   </si>
   <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>Gary Harris</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Bobby Portis</t>
-  </si>
-  <si>
-    <t>Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Tidjane Salaun</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Keegan Murray</t>
-  </si>
-  <si>
-    <t>Russell Westbrook</t>
-  </si>
-  <si>
-    <t>Isaiah Jackson</t>
-  </si>
-  <si>
-    <t>Thanasis Antetokounmpo</t>
-  </si>
-  <si>
     <t>Norman Powell</t>
   </si>
   <si>
-    <t>TJ McConnell</t>
-  </si>
-  <si>
-    <t>Andrew Nembhard</t>
-  </si>
-  <si>
-    <t>Pascal Siakam</t>
-  </si>
-  <si>
-    <t>Jarace Walker</t>
-  </si>
-  <si>
-    <t>Isaiah Stevens</t>
-  </si>
-  <si>
-    <t>Josh Minott</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Danny Wolf</t>
-  </si>
-  <si>
-    <t>Leaky Black</t>
-  </si>
-  <si>
     <t>WAS</t>
   </si>
   <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
     <t>Anthony Davis</t>
   </si>
   <si>
@@ -216,97 +132,157 @@
     <t>Trae Young</t>
   </si>
   <si>
-    <t>Robert Williams</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Jerami Grant</t>
-  </si>
-  <si>
-    <t>Vit Krejci</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jonathan Issac</t>
-  </si>
-  <si>
-    <t>Franz Wagner</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Trayce Jackson-Davis</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
-    <t>Chucky Hepburn</t>
-  </si>
-  <si>
-    <t>Immanual Quickley</t>
-  </si>
-  <si>
-    <t>Jayson Tatum</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>Trey Murphy III</t>
-  </si>
-  <si>
-    <t>NOP</t>
-  </si>
-  <si>
-    <t>Dejounte Murray</t>
-  </si>
-  <si>
-    <t>Bryce McGowens</t>
-  </si>
-  <si>
-    <t>Kevin McCullar</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>Miles McBride</t>
-  </si>
-  <si>
-    <t>Landry Shamet</t>
-  </si>
-  <si>
-    <t>Seth Curry</t>
-  </si>
-  <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>Quinten Post</t>
-  </si>
-  <si>
-    <t>Will Richard</t>
-  </si>
-  <si>
-    <t>Stephen Curry</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Nick Richards</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Guerschon Yabusele</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Dillon Brooks</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Amir Coffey</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Walter Clayton Jr.</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>DeJon Jarreau</t>
+  </si>
+  <si>
+    <t>Taj Gibson</t>
+  </si>
+  <si>
+    <t>Olivier-Maxence Prosper</t>
+  </si>
+  <si>
+    <t>Javon Small</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>Jaylen Wells</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Marvin Bagley</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>Craig Porter</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Max Strus</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Ausar Thompson</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Jalen Duren</t>
+  </si>
+  <si>
+    <t>Tobias Harris</t>
+  </si>
+  <si>
+    <t>Duncan Robinson</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Bub Carrington</t>
+  </si>
+  <si>
+    <t>D'Angelo Russell</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Adou Thiero</t>
   </si>
 </sst>
 </file>
@@ -816,7 +792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -856,27 +832,27 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -884,13 +860,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -898,13 +874,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -912,125 +888,125 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1038,13 +1014,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1052,69 +1028,69 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -1122,27 +1098,27 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1150,108 +1126,108 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>64</v>
@@ -1262,10 +1238,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>64</v>
@@ -1276,10 +1252,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>64</v>
@@ -1290,13 +1266,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -1304,13 +1280,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -1318,13 +1294,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -1332,13 +1308,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -1346,55 +1322,55 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -1402,27 +1378,27 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -1430,13 +1406,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -1444,13 +1420,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -1458,69 +1434,69 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
@@ -1528,113 +1504,29 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>84</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" s="9">
-        <v>46110</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A53" s="9">
-        <v>46110</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A54" s="9">
-        <v>46110</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A55" s="9">
-        <v>46110</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A56" s="9">
-        <v>46110</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A57" s="9">
-        <v>46110</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1648,7 +1540,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D297</xm:sqref>
+          <xm:sqref>D2:D241</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9954A1F1-07E9-4149-89DF-97FDB2672704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB45623-5B47-4F60-A849-7DBD475DB302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="88">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -102,9 +102,6 @@
     <t>BOS</t>
   </si>
   <si>
-    <t>Jaylen Brown</t>
-  </si>
-  <si>
     <t>Derrick White</t>
   </si>
   <si>
@@ -189,9 +186,6 @@
     <t>Jaylen Wells</t>
   </si>
   <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
     <t>MIN</t>
   </si>
   <si>
@@ -283,6 +277,18 @@
   </si>
   <si>
     <t>Adou Thiero</t>
+  </si>
+  <si>
+    <t>Jayson Tatum</t>
+  </si>
+  <si>
+    <t>Ron Harper Jr.</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>P.J. Washington</t>
   </si>
 </sst>
 </file>
@@ -792,7 +798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -835,10 +841,10 @@
         <v>46111</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -849,10 +855,10 @@
         <v>46111</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -863,13 +869,13 @@
         <v>46111</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -877,13 +883,13 @@
         <v>46111</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -905,10 +911,10 @@
         <v>46111</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -919,10 +925,10 @@
         <v>46111</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -933,10 +939,10 @@
         <v>46111</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -947,10 +953,10 @@
         <v>46111</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -961,10 +967,10 @@
         <v>46111</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -975,10 +981,10 @@
         <v>46111</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -989,10 +995,10 @@
         <v>46111</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1003,10 +1009,10 @@
         <v>46111</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1017,10 +1023,10 @@
         <v>46111</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1031,10 +1037,10 @@
         <v>46111</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -1045,10 +1051,10 @@
         <v>46111</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1059,10 +1065,10 @@
         <v>46111</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -1073,10 +1079,10 @@
         <v>46111</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1087,10 +1093,10 @@
         <v>46111</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -1100,11 +1106,11 @@
       <c r="A21" s="9">
         <v>46111</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>55</v>
+      <c r="C21" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1114,39 +1120,39 @@
       <c r="A22" s="9">
         <v>46111</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>55</v>
       </c>
+      <c r="C22" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
         <v>46111</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
         <v>46111</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>59</v>
+      <c r="C24" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -1156,67 +1162,67 @@
       <c r="A25" s="9">
         <v>46111</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
+      <c r="C25" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
         <v>46111</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>59</v>
+      <c r="B26" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
         <v>46111</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
         <v>46111</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>64</v>
+      <c r="C28" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
         <v>46111</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>64</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -1226,11 +1232,11 @@
       <c r="A30" s="9">
         <v>46111</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>64</v>
+      <c r="B30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -1240,11 +1246,11 @@
       <c r="A31" s="9">
         <v>46111</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>64</v>
+      <c r="B31" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -1254,11 +1260,11 @@
       <c r="A32" s="9">
         <v>46111</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -1268,11 +1274,11 @@
       <c r="A33" s="9">
         <v>46111</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>70</v>
+      <c r="C33" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -1282,11 +1288,11 @@
       <c r="A34" s="9">
         <v>46111</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>70</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -1296,39 +1302,39 @@
       <c r="A35" s="9">
         <v>46111</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
         <v>46111</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>74</v>
+      <c r="C36" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
         <v>46111</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>74</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
@@ -1338,11 +1344,11 @@
       <c r="A38" s="9">
         <v>46111</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>74</v>
+      <c r="B38" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
@@ -1352,25 +1358,25 @@
       <c r="A39" s="9">
         <v>46111</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>74</v>
+      <c r="B39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
         <v>46111</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>74</v>
+      <c r="B40" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -1380,25 +1386,25 @@
       <c r="A41" s="9">
         <v>46111</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>74</v>
+      <c r="B41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
         <v>46111</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>29</v>
+      <c r="B42" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -1408,11 +1414,11 @@
       <c r="A43" s="9">
         <v>46111</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>29</v>
+      <c r="C43" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -1422,39 +1428,39 @@
       <c r="A44" s="9">
         <v>46111</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>29</v>
+      <c r="C44" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
         <v>46111</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>29</v>
       </c>
+      <c r="C45" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
         <v>46111</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>29</v>
+      <c r="C46" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -1464,11 +1470,11 @@
       <c r="A47" s="9">
         <v>46111</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>29</v>
+      <c r="B47" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -1478,11 +1484,11 @@
       <c r="A48" s="9">
         <v>46111</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
@@ -1492,11 +1498,11 @@
       <c r="A49" s="9">
         <v>46111</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>83</v>
+      <c r="C49" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
@@ -1506,11 +1512,11 @@
       <c r="A50" s="9">
         <v>46111</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>83</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
@@ -1520,14 +1526,42 @@
       <c r="A51" s="9">
         <v>46111</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>83</v>
+      <c r="C51" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46111</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>46111</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1574,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D241</xm:sqref>
+          <xm:sqref>D2:D240</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB45623-5B47-4F60-A849-7DBD475DB302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99576509-390D-4B34-9C16-16637568FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="81">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,57 +96,6 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>Norman Powell</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>Anthony Davis</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Alex Sarr</t>
-  </si>
-  <si>
-    <t>Trae Young</t>
-  </si>
-  <si>
-    <t>Johni Broome</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Nick Richards</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>Guerschon Yabusele</t>
-  </si>
-  <si>
-    <t>Anfernee Simons</t>
-  </si>
-  <si>
     <t>Dillon Brooks</t>
   </si>
   <si>
@@ -162,42 +111,6 @@
     <t>Mark Williams</t>
   </si>
   <si>
-    <t>Walter Clayton Jr.</t>
-  </si>
-  <si>
-    <t>MEM</t>
-  </si>
-  <si>
-    <t>DeJon Jarreau</t>
-  </si>
-  <si>
-    <t>Taj Gibson</t>
-  </si>
-  <si>
-    <t>Olivier-Maxence Prosper</t>
-  </si>
-  <si>
-    <t>Javon Small</t>
-  </si>
-  <si>
-    <t>Ty Jerome</t>
-  </si>
-  <si>
-    <t>Jaylen Wells</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
     <t>DAL</t>
   </si>
   <si>
@@ -210,9 +123,6 @@
     <t>Caleb Martin</t>
   </si>
   <si>
-    <t>Craig Porter</t>
-  </si>
-  <si>
     <t>CLE</t>
   </si>
   <si>
@@ -228,21 +138,6 @@
     <t>Dean Wade</t>
   </si>
   <si>
-    <t>Isaiah Collier</t>
-  </si>
-  <si>
-    <t>UTA</t>
-  </si>
-  <si>
-    <t>Keyonte George</t>
-  </si>
-  <si>
-    <t>Lauri Markkanen</t>
-  </si>
-  <si>
-    <t>Ausar Thompson</t>
-  </si>
-  <si>
     <t>DET</t>
   </si>
   <si>
@@ -261,12 +156,6 @@
     <t>Isaiah Stewart</t>
   </si>
   <si>
-    <t>Bub Carrington</t>
-  </si>
-  <si>
-    <t>D'Angelo Russell</t>
-  </si>
-  <si>
     <t>Luka Doncic</t>
   </si>
   <si>
@@ -279,16 +168,106 @@
     <t>Adou Thiero</t>
   </si>
   <si>
-    <t>Jayson Tatum</t>
-  </si>
-  <si>
-    <t>Ron Harper Jr.</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
     <t>P.J. Washington</t>
+  </si>
+  <si>
+    <t>Grayson Allen</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>Franz Wagner</t>
+  </si>
+  <si>
+    <t>Jalen Wilson</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Terance Mann</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Jamison Battle</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Miles McBride</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Landry Shamet</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Gary Harris</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -798,7 +777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -838,27 +817,27 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>35</v>
+        <v>46112</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>26</v>
+        <v>46112</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -866,83 +845,83 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="7" t="s">
+        <v>46112</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="6" t="s">
+        <v>46112</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
+        <v>46112</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>46112</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>37</v>
+        <v>46112</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>46112</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -950,27 +929,27 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>41</v>
+        <v>46112</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>41</v>
+        <v>46112</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -978,13 +957,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>41</v>
+        <v>46112</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -992,13 +971,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>41</v>
+        <v>46112</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1006,27 +985,27 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1034,55 +1013,55 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1090,13 +1069,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>46</v>
+        <v>46112</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -1104,27 +1083,27 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -1132,41 +1111,41 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1174,125 +1153,125 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -1300,69 +1279,69 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -1370,13 +1349,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -1384,69 +1363,69 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -1454,13 +1433,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -1468,100 +1447,16 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A51" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A53" s="9">
-        <v>46111</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1574,7 +1469,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D240</xm:sqref>
+          <xm:sqref>D2:D188</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99576509-390D-4B34-9C16-16637568FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D31EC7-86EF-474B-BE5D-F4BEDF4202AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
   </si>
   <si>
     <t>LAL</t>
@@ -777,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -834,7 +831,7 @@
         <v>46112</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>24</v>
@@ -890,10 +887,10 @@
         <v>46112</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -904,10 +901,10 @@
         <v>46112</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -918,10 +915,10 @@
         <v>46112</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -932,10 +929,10 @@
         <v>46112</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -946,10 +943,10 @@
         <v>46112</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -960,10 +957,10 @@
         <v>46112</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -974,10 +971,10 @@
         <v>46112</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -988,10 +985,10 @@
         <v>46112</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -1002,10 +999,10 @@
         <v>46112</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1016,10 +1013,10 @@
         <v>46112</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1030,10 +1027,10 @@
         <v>46112</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -1044,10 +1041,10 @@
         <v>46112</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -1058,10 +1055,10 @@
         <v>46112</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1092,7 +1089,7 @@
         <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
@@ -1106,7 +1103,7 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
@@ -1120,7 +1117,7 @@
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -1142,10 +1139,10 @@
         <v>46112</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1156,10 +1153,10 @@
         <v>46112</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -1170,7 +1167,7 @@
         <v>46112</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>28</v>
@@ -1226,10 +1223,10 @@
         <v>46112</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -1240,10 +1237,10 @@
         <v>46112</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -1254,10 +1251,10 @@
         <v>46112</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1268,10 +1265,10 @@
         <v>46112</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -1282,10 +1279,10 @@
         <v>46112</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -1296,10 +1293,10 @@
         <v>46112</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -1316,7 +1313,7 @@
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
@@ -1330,7 +1327,7 @@
         <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
@@ -1365,39 +1362,39 @@
       <c r="A41" s="9">
         <v>46112</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
         <v>46112</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>44</v>
+      <c r="C42" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
         <v>46112</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>44</v>
+      <c r="B43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -1407,11 +1404,11 @@
       <c r="A44" s="9">
         <v>46112</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -1421,11 +1418,11 @@
       <c r="A45" s="9">
         <v>46112</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>76</v>
+      <c r="C45" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -1435,27 +1432,13 @@
       <c r="A46" s="9">
         <v>46112</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>76</v>
+      <c r="C46" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1469,7 +1452,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D188</xm:sqref>
+          <xm:sqref>D2:D187</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D31EC7-86EF-474B-BE5D-F4BEDF4202AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F776EE-8CDF-4013-81E1-F20CDA944763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="90">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,81 +96,6 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Dillon Brooks</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Amir Coffey</t>
-  </si>
-  <si>
-    <t>Haywood Highsmith</t>
-  </si>
-  <si>
-    <t>Mark Williams</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>Marvin Bagley</t>
-  </si>
-  <si>
-    <t>Caleb Martin</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>Max Strus</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Jalen Duren</t>
-  </si>
-  <si>
-    <t>Tobias Harris</t>
-  </si>
-  <si>
-    <t>Duncan Robinson</t>
-  </si>
-  <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
-    <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Adou Thiero</t>
-  </si>
-  <si>
-    <t>P.J. Washington</t>
-  </si>
-  <si>
-    <t>Grayson Allen</t>
-  </si>
-  <si>
     <t>Anthony Black</t>
   </si>
   <si>
@@ -183,33 +108,9 @@
     <t>Franz Wagner</t>
   </si>
   <si>
-    <t>Jalen Wilson</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>Terance Mann</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Danny Wolf</t>
-  </si>
-  <si>
-    <t>RJ Barrett</t>
-  </si>
-  <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>Collin Murray-Boyles</t>
-  </si>
-  <si>
     <t>Jamison Battle</t>
   </si>
   <si>
@@ -219,24 +120,15 @@
     <t>Immanuel Quickley</t>
   </si>
   <si>
-    <t>Miles McBride</t>
-  </si>
-  <si>
     <t>NYK</t>
   </si>
   <si>
     <t>Landry Shamet</t>
   </si>
   <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
     <t>MIL</t>
   </si>
   <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
     <t>Gary Harris</t>
   </si>
   <si>
@@ -249,22 +141,160 @@
     <t>Bobby Portis</t>
   </si>
   <si>
-    <t>Jerami Grant</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Vit Krejci</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
-    <t>Isaiah Jackson</t>
-  </si>
-  <si>
-    <t>LAC</t>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Kyshawn George</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Ron Harper Jr.</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>Andrew Wiggins</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Norman Powell</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Obi Toppin</t>
+  </si>
+  <si>
+    <t>TJ McConnell</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>Nick Richards</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Guerschon Yabusele</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Keegan Murray</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Russell Westbrook</t>
+  </si>
+  <si>
+    <t>Taj Gibson</t>
+  </si>
+  <si>
+    <t>Taylor Hendricks</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Spencer Jones</t>
+  </si>
+  <si>
+    <t>Zeke Nnaji</t>
+  </si>
+  <si>
+    <t>Elijah Harkless</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Luke Kornet</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Gary Payton II</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>De'Anthony Melton</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
   </si>
 </sst>
 </file>
@@ -774,7 +804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -814,24 +844,24 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>24</v>
@@ -842,111 +872,111 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -954,27 +984,27 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -982,69 +1012,69 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -1052,13 +1082,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1066,13 +1096,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -1080,55 +1110,55 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -1136,13 +1166,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1150,181 +1180,181 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -1332,13 +1362,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -1346,13 +1376,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -1360,13 +1390,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>43</v>
+        <v>46113</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -1374,27 +1404,27 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>43</v>
+        <v>46113</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>75</v>
+        <v>46113</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -1402,13 +1432,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B44" s="7" t="s">
+        <v>46113</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -1416,13 +1446,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>75</v>
+        <v>46113</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -1430,15 +1460,99 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46112</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>79</v>
+        <v>46113</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="D46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1452,7 +1566,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D187</xm:sqref>
+          <xm:sqref>D2:D142</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F776EE-8CDF-4013-81E1-F20CDA944763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F905D05E-8D15-4FE5-B773-FCEEFE5907A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,177 +96,6 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>Franz Wagner</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Jamison Battle</t>
-  </si>
-  <si>
-    <t>Chucky Hepburn</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>Landry Shamet</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Gary Harris</t>
-  </si>
-  <si>
-    <t>Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Bobby Portis</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>MEM</t>
-  </si>
-  <si>
-    <t>Johni Broome</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
-    <t>Alex Sarr</t>
-  </si>
-  <si>
-    <t>Kyshawn George</t>
-  </si>
-  <si>
-    <t>Trae Young</t>
-  </si>
-  <si>
-    <t>Ron Harper Jr.</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>Andrew Wiggins</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>Norman Powell</t>
-  </si>
-  <si>
-    <t>Pascal Siakam</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>Obi Toppin</t>
-  </si>
-  <si>
-    <t>TJ McConnell</t>
-  </si>
-  <si>
-    <t>Andrew Nembhard</t>
-  </si>
-  <si>
-    <t>Aaron Nesmith</t>
-  </si>
-  <si>
-    <t>Jarace Walker</t>
-  </si>
-  <si>
-    <t>Nick Richards</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>Guerschon Yabusele</t>
-  </si>
-  <si>
-    <t>Anfernee Simons</t>
-  </si>
-  <si>
-    <t>Keegan Murray</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Russell Westbrook</t>
-  </si>
-  <si>
-    <t>Taj Gibson</t>
-  </si>
-  <si>
-    <t>Taylor Hendricks</t>
-  </si>
-  <si>
-    <t>Ty Jerome</t>
-  </si>
-  <si>
-    <t>Aaron Gordon</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Spencer Jones</t>
-  </si>
-  <si>
-    <t>Zeke Nnaji</t>
-  </si>
-  <si>
-    <t>Elijah Harkless</t>
-  </si>
-  <si>
-    <t>UTA</t>
-  </si>
-  <si>
-    <t>Isaiah Collier</t>
-  </si>
-  <si>
-    <t>Keyonte George</t>
-  </si>
-  <si>
-    <t>Lauri Markkanen</t>
-  </si>
-  <si>
     <t>Luke Kornet</t>
   </si>
   <si>
@@ -295,6 +124,96 @@
   </si>
   <si>
     <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Marcus Sasser</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Amir Coffey</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>PJ Hall</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Alex Caruso</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Karlo Matkovic</t>
+  </si>
+  <si>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>Trey Murphy III</t>
+  </si>
+  <si>
+    <t>Bryce McGowens</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -804,7 +723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -844,13 +763,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>39</v>
+        <v>46114</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -858,55 +777,55 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>24</v>
+        <v>46114</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
+        <v>46114</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>24</v>
+        <v>46114</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>46114</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -914,13 +833,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>46114</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -928,41 +847,41 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>43</v>
+        <v>46114</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="7" t="s">
+        <v>46114</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="C9" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>46114</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -970,13 +889,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B11" s="7" t="s">
+        <v>46114</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -984,12 +903,12 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B12" s="6" t="s">
+        <v>46114</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D12" t="s">
@@ -998,13 +917,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B13" s="7" t="s">
+        <v>46114</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>49</v>
+      <c r="C13" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1012,111 +931,111 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B14" s="6" t="s">
+        <v>46114</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>52</v>
+        <v>46114</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>55</v>
+        <v>46114</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>55</v>
+        <v>46114</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>55</v>
+        <v>46114</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>55</v>
+        <v>46114</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>46114</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>55</v>
+        <v>46114</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -1124,13 +1043,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>62</v>
+        <v>46114</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1138,13 +1057,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>62</v>
+        <v>46114</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1152,13 +1071,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>62</v>
+        <v>46114</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -1166,393 +1085,71 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>33</v>
+        <v>46114</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>33</v>
+        <v>46114</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>33</v>
+        <v>46114</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>33</v>
+        <v>46114</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>66</v>
+        <v>46114</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A51" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" s="9">
-        <v>46113</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1566,7 +1163,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D142</xm:sqref>
+          <xm:sqref>D2:D91</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F905D05E-8D15-4FE5-B773-FCEEFE5907A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF25D9D0-6CAB-47B2-855D-B2C68C607549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="90">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,36 +96,6 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Luke Kornet</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Gary Payton II</t>
-  </si>
-  <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>Stephen Curry</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>De'Anthony Melton</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
-    <t>Quinten Post</t>
-  </si>
-  <si>
     <t>Anthony Edwards</t>
   </si>
   <si>
@@ -135,85 +105,196 @@
     <t>Jaden McDaniels</t>
   </si>
   <si>
-    <t>Marcus Sasser</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
-    <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>Mark Williams</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Amir Coffey</t>
-  </si>
-  <si>
-    <t>Haywood Highsmith</t>
-  </si>
-  <si>
     <t>PJ Hall</t>
   </si>
   <si>
     <t>CHA</t>
   </si>
   <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Alex Caruso</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
     <t>Karlo Matkovic</t>
   </si>
   <si>
     <t>NOP</t>
   </si>
   <si>
-    <t>Trey Murphy III</t>
-  </si>
-  <si>
     <t>Bryce McGowens</t>
   </si>
   <si>
-    <t>Jerami Grant</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Vit Krejci</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
-    <t>Isaiah Jackson</t>
-  </si>
-  <si>
-    <t>LAC</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>Obi Toppin</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>TJ McConnell</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>Mac McClung</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Lachlan Olbrich</t>
+  </si>
+  <si>
+    <t>Guerschon Yabusele</t>
+  </si>
+  <si>
+    <t>Josh Giddey</t>
+  </si>
+  <si>
+    <t>Tre Jones</t>
+  </si>
+  <si>
+    <t>Nick Richards</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Eiljah Harkless</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Ryan Rolling</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Jericho Sims</t>
+  </si>
+  <si>
+    <t>Gary Trent</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Jamison Battle</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Taj Gibson</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>Olivier-Maxence Prosper</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>Cam Spencer</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>Marvin Bagley</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>P.J. Washington</t>
+  </si>
+  <si>
+    <t>Malik Monk</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Keegan Murray</t>
+  </si>
+  <si>
+    <t>Russell Westbrook</t>
   </si>
 </sst>
 </file>
@@ -723,7 +804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -763,13 +844,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -777,13 +858,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -791,27 +872,27 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -819,41 +900,41 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -861,13 +942,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -875,13 +956,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -889,13 +970,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -903,13 +984,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -917,13 +998,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -931,125 +1012,125 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1057,13 +1138,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1071,13 +1152,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -1085,13 +1166,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -1099,13 +1180,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -1113,13 +1194,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -1127,21 +1208,21 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>61</v>
@@ -1150,6 +1231,328 @@
         <v>62</v>
       </c>
       <c r="D29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46115</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1163,7 +1566,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D91</xm:sqref>
+          <xm:sqref>D2:D63</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF25D9D0-6CAB-47B2-855D-B2C68C607549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7709D30F-61BD-4BD2-A6BD-5C59817E1925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,30 +96,6 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>PJ Hall</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>Karlo Matkovic</t>
-  </si>
-  <si>
-    <t>NOP</t>
-  </si>
-  <si>
-    <t>Bryce McGowens</t>
-  </si>
-  <si>
     <t>Joel Embiid</t>
   </si>
   <si>
@@ -129,172 +105,76 @@
     <t>Johni Broome</t>
   </si>
   <si>
-    <t>Obi Toppin</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>Pascal Siakam</t>
-  </si>
-  <si>
-    <t>TJ McConnell</t>
-  </si>
-  <si>
-    <t>Andrew Nembhard</t>
-  </si>
-  <si>
-    <t>Aaron Nesmith</t>
-  </si>
-  <si>
-    <t>Jarace Walker</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>Nic Claxton</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
-    <t>Danny Wolf</t>
-  </si>
-  <si>
-    <t>Mac McClung</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>Lachlan Olbrich</t>
-  </si>
-  <si>
-    <t>Guerschon Yabusele</t>
-  </si>
-  <si>
-    <t>Josh Giddey</t>
-  </si>
-  <si>
-    <t>Tre Jones</t>
-  </si>
-  <si>
-    <t>Nick Richards</t>
-  </si>
-  <si>
-    <t>Anfernee Simons</t>
-  </si>
-  <si>
-    <t>Isaiah Collier</t>
-  </si>
-  <si>
-    <t>UTA</t>
-  </si>
-  <si>
-    <t>Keyonte George</t>
-  </si>
-  <si>
-    <t>Eiljah Harkless</t>
-  </si>
-  <si>
-    <t>Lauri Markkanen</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Ryan Rolling</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Jericho Sims</t>
-  </si>
-  <si>
-    <t>Gary Trent</t>
-  </si>
-  <si>
-    <t>Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Bobby Portis</t>
-  </si>
-  <si>
-    <t>Jamison Battle</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Chucky Hepburn</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Taj Gibson</t>
-  </si>
-  <si>
-    <t>MEM</t>
-  </si>
-  <si>
-    <t>Olivier-Maxence Prosper</t>
-  </si>
-  <si>
-    <t>Ty Jerome</t>
-  </si>
-  <si>
-    <t>Cam Spencer</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>Marvin Bagley</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>Caleb Martin</t>
-  </si>
-  <si>
-    <t>P.J. Washington</t>
-  </si>
-  <si>
-    <t>Malik Monk</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Keegan Murray</t>
-  </si>
-  <si>
-    <t>Russell Westbrook</t>
+    <t>Emanuel Miller</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Spencer Jones</t>
+  </si>
+  <si>
+    <t>Zeke Nnaji</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>Justin Champagnie</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Tyler Herro</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Norman Powell</t>
+  </si>
+  <si>
+    <t>Marcus Sasser</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Tobias Harris</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Paul George</t>
   </si>
 </sst>
 </file>
@@ -804,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -844,55 +724,55 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>24</v>
+        <v>46116</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>46116</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>32</v>
+        <v>46116</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>32</v>
+        <v>46116</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -900,111 +780,111 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>35</v>
+        <v>46116</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>35</v>
+        <v>46116</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="7" t="s">
+        <v>46116</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
+      <c r="C8" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>46116</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>35</v>
+        <v>46116</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>35</v>
+        <v>46116</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>27</v>
+        <v>46116</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>42</v>
+        <v>46116</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1012,13 +892,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>44</v>
+        <v>46116</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -1026,97 +906,97 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>44</v>
+        <v>46116</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="7" t="s">
+        <v>46116</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>44</v>
       </c>
+      <c r="C16" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>44</v>
+        <v>46116</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>49</v>
+        <v>46116</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>49</v>
+        <v>46116</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>49</v>
+        <v>46116</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="6" t="s">
+        <v>46116</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1124,435 +1004,15 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>49</v>
+        <v>46116</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A51" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D52" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1566,7 +1026,7 @@
           <x14:formula1>
             <xm:f>status_reference!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D63</xm:sqref>
+          <xm:sqref>D2:D12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7709D30F-61BD-4BD2-A6BD-5C59817E1925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E296A298-0687-472A-9361-D34C40CD0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="117">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,48 +96,9 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Johni Broome</t>
-  </si>
-  <si>
-    <t>Emanuel Miller</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Tim Hardaway Jr.</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Spencer Jones</t>
-  </si>
-  <si>
-    <t>Zeke Nnaji</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
-  </si>
-  <si>
-    <t>Justin Champagnie</t>
-  </si>
-  <si>
     <t>WAS</t>
   </si>
   <si>
-    <t>Bilal Coulibaly</t>
-  </si>
-  <si>
-    <t>Tre Johnson</t>
-  </si>
-  <si>
     <t>Alex Sarr</t>
   </si>
   <si>
@@ -150,31 +111,271 @@
     <t>Trae Young</t>
   </si>
   <si>
-    <t>Tyler Herro</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>Norman Powell</t>
-  </si>
-  <si>
-    <t>Marcus Sasser</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Tobias Harris</t>
-  </si>
-  <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
-    <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>Paul George</t>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Amir Coffey</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>Lachlan Olbrich</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Collin Sexton</t>
+  </si>
+  <si>
+    <t>Josh Giddey</t>
+  </si>
+  <si>
+    <t>Nick Richards</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Taj Gibson</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>Walter Clayton Jr.</t>
+  </si>
+  <si>
+    <t>Cedric Coward</t>
+  </si>
+  <si>
+    <t>GG Jackson</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>Jahmai Mashack</t>
+  </si>
+  <si>
+    <t>Javon Small</t>
+  </si>
+  <si>
+    <t>Cam Spencer</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Gary Trent</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Terance Mann</t>
+  </si>
+  <si>
+    <t>Ben Saraf</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Ziaire Williams</t>
+  </si>
+  <si>
+    <t>Obi Toppin</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Ben Sheppard</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>TJ McConnell</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Anthony Black</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>Bryce McGowens</t>
+  </si>
+  <si>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>Karlo Matkovic</t>
+  </si>
+  <si>
+    <t>Trey Murphy III</t>
+  </si>
+  <si>
+    <t>Dejounte Murray</t>
+  </si>
+  <si>
+    <t>Moussa Diabate</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>PJ Hall</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Elijah Harkless</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Jarred Vanderbilt</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Marvin Bagley</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Tyler Smith</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>Keegan Murray</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Isaiah Stevens</t>
+  </si>
+  <si>
+    <t>Russell Westbrook</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Seth Curry</t>
+  </si>
+  <si>
+    <t>Steven Curry</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
   </si>
 </sst>
 </file>
@@ -194,22 +395,26 @@
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -684,7 +889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -724,13 +929,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>27</v>
+        <v>46117</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -738,55 +943,55 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="7" t="s">
+        <v>46117</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>46117</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>29</v>
+        <v>46117</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>29</v>
+        <v>46117</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -794,41 +999,41 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>34</v>
+        <v>46117</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>46117</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>34</v>
+        <v>46117</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -836,13 +1041,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B10" s="6" t="s">
+        <v>46117</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -850,111 +1055,111 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>34</v>
+        <v>46117</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>34</v>
+        <v>46117</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>34</v>
+        <v>46117</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>42</v>
+        <v>46117</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B15" s="7" t="s">
+        <v>46117</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>45</v>
+        <v>46117</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>45</v>
+        <v>46117</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>45</v>
+        <v>46117</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -962,13 +1167,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>45</v>
+        <v>46117</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -976,13 +1181,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>24</v>
+        <v>46117</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -990,47 +1195,777 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>24</v>
+        <v>46117</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B22" s="6" t="s">
+        <v>46117</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" error="Use one of: Probable, Questionable, Doubtful, Out" prompt="Select a status" xr:uid="{00000000-0002-0000-0100-000000000000}">
-          <x14:formula1>
-            <xm:f>status_reference!$A$2:$A$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D12</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E296A298-0687-472A-9361-D34C40CD0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C83BB35-B361-486D-BDA9-474868BD73EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,72 +96,9 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>Alex Sarr</t>
-  </si>
-  <si>
-    <t>Tristan Vukcevic</t>
-  </si>
-  <si>
-    <t>Anthony Davis</t>
-  </si>
-  <si>
-    <t>Trae Young</t>
-  </si>
-  <si>
-    <t>Chucky Hepburn</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Nikola Vucevic</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Amir Coffey</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Haywood Highsmith</t>
-  </si>
-  <si>
-    <t>Lachlan Olbrich</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>Collin Sexton</t>
-  </si>
-  <si>
-    <t>Josh Giddey</t>
-  </si>
-  <si>
-    <t>Nick Richards</t>
-  </si>
-  <si>
-    <t>Anfernee Simons</t>
-  </si>
-  <si>
-    <t>Taj Gibson</t>
-  </si>
-  <si>
     <t>MEM</t>
   </si>
   <si>
-    <t>Walter Clayton Jr.</t>
-  </si>
-  <si>
     <t>Cedric Coward</t>
   </si>
   <si>
@@ -180,66 +117,6 @@
     <t>Cam Spencer</t>
   </si>
   <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t>Kevin Porter Jr.</t>
-  </si>
-  <si>
-    <t>Bobby Portis</t>
-  </si>
-  <si>
-    <t>Gary Trent</t>
-  </si>
-  <si>
-    <t>Noah Clowney</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>Terance Mann</t>
-  </si>
-  <si>
-    <t>Ben Saraf</t>
-  </si>
-  <si>
-    <t>Nic Claxton</t>
-  </si>
-  <si>
-    <t>Ziaire Williams</t>
-  </si>
-  <si>
-    <t>Obi Toppin</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>Ben Sheppard</t>
-  </si>
-  <si>
-    <t>Jarace Walker</t>
-  </si>
-  <si>
-    <t>TJ McConnell</t>
-  </si>
-  <si>
-    <t>Andrew Nembhard</t>
-  </si>
-  <si>
-    <t>Aaron Nesmith</t>
-  </si>
-  <si>
-    <t>Pascal Siakam</t>
-  </si>
-  <si>
     <t>Jarrett Allen</t>
   </si>
   <si>
@@ -267,115 +144,70 @@
     <t>Jonathan Isaac</t>
   </si>
   <si>
-    <t>Bryce McGowens</t>
-  </si>
-  <si>
-    <t>NOP</t>
-  </si>
-  <si>
-    <t>Karlo Matkovic</t>
-  </si>
-  <si>
-    <t>Trey Murphy III</t>
-  </si>
-  <si>
-    <t>Dejounte Murray</t>
-  </si>
-  <si>
-    <t>Moussa Diabate</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>PJ Hall</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Isaiah Collier</t>
-  </si>
-  <si>
-    <t>UTA</t>
-  </si>
-  <si>
-    <t>Keyonte George</t>
-  </si>
-  <si>
-    <t>Elijah Harkless</t>
-  </si>
-  <si>
-    <t>Lauri Markkanen</t>
-  </si>
-  <si>
-    <t>Jarred Vanderbilt</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
-    <t>Marvin Bagley</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>Tyler Smith</t>
-  </si>
-  <si>
-    <t>Caleb Martin</t>
-  </si>
-  <si>
-    <t>Isaiah Jackson</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>Keegan Murray</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Isaiah Stevens</t>
-  </si>
-  <si>
-    <t>Russell Westbrook</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>Seth Curry</t>
-  </si>
-  <si>
-    <t>Steven Curry</t>
-  </si>
-  <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Quinten Post</t>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Tobias Harris</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Duncan Robinson</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Jett Howard</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Cameron Payne</t>
+  </si>
+  <si>
+    <t>Emanuel Miller</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>Bruce Brown</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Zeke Nnaji</t>
+  </si>
+  <si>
+    <t>Spencer Jones</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
   </si>
 </sst>
 </file>
@@ -889,7 +721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -929,13 +761,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -943,27 +775,27 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -971,27 +803,27 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -999,7 +831,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>36</v>
@@ -1008,60 +840,60 @@
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1069,69 +901,69 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -1139,13 +971,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -1153,41 +985,41 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1195,83 +1027,83 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -1279,687 +1111,57 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A51" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A53" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A54" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A55" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A56" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A57" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A58" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A59" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A60" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A61" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A62" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A63" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D68" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D69" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D70" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D71" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C83BB35-B361-486D-BDA9-474868BD73EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2589A5D-EACE-4DA7-923F-1FA4D529F1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="116">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,118 +96,283 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>MEM</t>
-  </si>
-  <si>
-    <t>Cedric Coward</t>
-  </si>
-  <si>
-    <t>GG Jackson</t>
-  </si>
-  <si>
-    <t>Ty Jerome</t>
-  </si>
-  <si>
-    <t>Jahmai Mashack</t>
-  </si>
-  <si>
-    <t>Javon Small</t>
-  </si>
-  <si>
-    <t>Cam Spencer</t>
-  </si>
-  <si>
-    <t>Jarrett Allen</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>Evan Mobley</t>
-  </si>
-  <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
-    <t>Anthony Black</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Tobias Harris</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Duncan Robinson</t>
-  </si>
-  <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
-    <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>Jett Howard</t>
-  </si>
-  <si>
-    <t>Johni Broome</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Cameron Payne</t>
-  </si>
-  <si>
-    <t>Emanuel Miller</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Jerami Grant</t>
-  </si>
-  <si>
-    <t>Vit Krejci</t>
-  </si>
-  <si>
-    <t>Bruce Brown</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Zeke Nnaji</t>
-  </si>
-  <si>
-    <t>Spencer Jones</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Obi Toppin</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Ben Sheppard</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>TJ McConnell</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Lachlan Olbrich</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Collin Sexton</t>
+  </si>
+  <si>
+    <t>Matas Buzelis</t>
+  </si>
+  <si>
+    <t>Josh Giddey</t>
+  </si>
+  <si>
+    <t>Nick Richards</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Justin Champagnie</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Kevin Porter Jr.</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Gary Trent</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Ben Saraf</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>Tre Mann</t>
+  </si>
+  <si>
+    <t>Ziaire Williams</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>Tyler Herro</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Norman Powell</t>
+  </si>
+  <si>
+    <t>Nikola Jovic</t>
+  </si>
+  <si>
+    <t>Sandro Mamukelashvili</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Coby White</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>PJ Hall</t>
+  </si>
+  <si>
+    <t>Ace Bailey</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Kyle Filipowski</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Elijah Harkless</t>
+  </si>
+  <si>
+    <t>Karlo Matkovic</t>
+  </si>
+  <si>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>Dejounte Murray</t>
+  </si>
+  <si>
+    <t>Bryce McGowens</t>
+  </si>
+  <si>
+    <t>Trey Murphy III</t>
+  </si>
+  <si>
+    <t>DeMar DeRozan</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Keegan Murray</t>
+  </si>
+  <si>
+    <t>Russell Westbrook</t>
+  </si>
+  <si>
+    <t>LJ Cryer</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Marvin Bagley</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Brandon Williams</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>PHX</t>
   </si>
 </sst>
 </file>
@@ -721,7 +886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -761,13 +926,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -775,69 +940,69 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -845,13 +1010,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -859,13 +1024,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -873,13 +1038,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -887,41 +1052,41 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -929,13 +1094,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -943,13 +1108,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -957,13 +1122,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -971,27 +1136,27 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -999,13 +1164,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1013,13 +1178,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1027,69 +1192,69 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -1097,13 +1262,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -1111,41 +1276,41 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -1153,15 +1318,659 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D76" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB0790B-92C1-46A3-A3E8-6173C39F75DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A170C0-8F85-4741-9C11-D31DE808E5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="88">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,169 +96,199 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Jaden McDaniels</t>
-  </si>
-  <si>
-    <t>Giannis Antetokounmpo</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Kyle Kuzma</t>
-  </si>
-  <si>
-    <t>Bobby Portis</t>
-  </si>
-  <si>
-    <t>Ryan Rollins</t>
-  </si>
-  <si>
-    <t>Gary Trent</t>
-  </si>
-  <si>
-    <t>Myles Turner</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>Brandon Williams</t>
-  </si>
-  <si>
-    <t>Daniel Gafford</t>
-  </si>
-  <si>
-    <t>Caleb Martin</t>
-  </si>
-  <si>
-    <t>Isaiah Jackson</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Haywood Highsmith</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>MEM</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Jaylen Tyson</t>
-  </si>
-  <si>
-    <t>Dean Wade</t>
-  </si>
-  <si>
-    <t>Thomas Bryant</t>
-  </si>
-  <si>
-    <t>Cade Cunningham</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Isaiah Stewart</t>
-  </si>
-  <si>
-    <t>Jamal Cain</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Wendell Carter Jr.</t>
-  </si>
-  <si>
-    <t>Jett Howard</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>Jahmai Mashack</t>
-  </si>
-  <si>
-    <t>Olivier-Maxence Prosper</t>
-  </si>
-  <si>
-    <t>GG Jackson</t>
-  </si>
-  <si>
-    <t>Ty Jerome</t>
-  </si>
-  <si>
-    <t>Javon Small</t>
-  </si>
-  <si>
-    <t>Cam Spencer</t>
-  </si>
-  <si>
-    <t>Spencer Jones</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
-  </si>
-  <si>
-    <t>Vit Krejci</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
-    <t>Jerami Grant</t>
-  </si>
-  <si>
-    <t>Emanuel Miller</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Stephon Castle</t>
-  </si>
-  <si>
-    <t>Victor Wembanyama</t>
-  </si>
-  <si>
-    <t>Naji Marshall</t>
-  </si>
-  <si>
-    <t>PJ Washington</t>
+    <t>Lachlan Olbrich</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Collin Sexton</t>
+  </si>
+  <si>
+    <t>Patrick Williams</t>
+  </si>
+  <si>
+    <t>Isaac Okoro</t>
+  </si>
+  <si>
+    <t>Matas Buzelis</t>
+  </si>
+  <si>
+    <t>Josh Giddey</t>
+  </si>
+  <si>
+    <t>Nick Richards</t>
+  </si>
+  <si>
+    <t>Anfernee Simons</t>
+  </si>
+  <si>
+    <t>Justin Champagnie</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>Anthony Gill</t>
+  </si>
+  <si>
+    <t>Jaden Hardy</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Tristan Vukcevic</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Norman Powell</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Dru Smith</t>
+  </si>
+  <si>
+    <t>Nikola Jovic</t>
+  </si>
+  <si>
+    <t>Chucky Hepburn</t>
+  </si>
+  <si>
+    <t>Kobe Brown</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Ben Sheppard</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>TJ McConnell</t>
+  </si>
+  <si>
+    <t>Andrew Nembhard</t>
+  </si>
+  <si>
+    <t>Aaron Nesmith</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Nic Claxton</t>
+  </si>
+  <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>Noah Clowney</t>
+  </si>
+  <si>
+    <t>Tre Mann</t>
+  </si>
+  <si>
+    <t>Josh Minott</t>
+  </si>
+  <si>
+    <t>Nolan Traore</t>
+  </si>
+  <si>
+    <t>Ziaire Williams</t>
+  </si>
+  <si>
+    <t>Danny Wolf</t>
+  </si>
+  <si>
+    <t>Michael Porter Jr.</t>
+  </si>
+  <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Tyler Kolek</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Cameron Payne</t>
+  </si>
+  <si>
+    <t>Marcus Smart</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>Jaxson Hayes</t>
+  </si>
+  <si>
+    <t>LJ Cryer</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Charles Bassey</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Gui Santos</t>
+  </si>
+  <si>
+    <t>Will Richard</t>
+  </si>
+  <si>
+    <t>Al Horford</t>
+  </si>
+  <si>
+    <t>Kristaps Porzingis</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
   </si>
 </sst>
 </file>
@@ -772,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -812,55 +842,55 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>45</v>
+        <v>46121</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>47</v>
+        <v>46121</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>47</v>
+        <v>46121</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>47</v>
+        <v>46121</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -868,13 +898,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>47</v>
+        <v>46121</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -882,55 +912,55 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>27</v>
+        <v>46121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>46121</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>27</v>
+        <v>46121</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B10" s="6" t="s">
+        <v>46121</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>27</v>
+      <c r="C10" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -938,13 +968,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>27</v>
+        <v>46121</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -952,27 +982,27 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
+        <v>46121</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>52</v>
+        <v>46121</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -980,13 +1010,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>52</v>
+        <v>46121</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -994,167 +1024,167 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>24</v>
+        <v>46121</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>24</v>
+        <v>46121</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>55</v>
+        <v>46121</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>55</v>
+        <v>46121</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>55</v>
+        <v>46121</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>46121</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>44</v>
+        <v>46121</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>44</v>
+        <v>46121</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>44</v>
+        <v>46121</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>44</v>
+        <v>46121</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>44</v>
+        <v>46121</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>44</v>
+        <v>46121</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -1162,13 +1192,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>66</v>
+        <v>46121</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -1176,13 +1206,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>66</v>
+        <v>46121</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -1190,41 +1220,41 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>69</v>
+        <v>46121</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>69</v>
+        <v>46121</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>69</v>
+        <v>46121</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -1232,69 +1262,69 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>73</v>
+        <v>46121</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>73</v>
+        <v>46121</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>73</v>
+        <v>46121</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>40</v>
+        <v>46121</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>38</v>
+        <v>46121</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -1302,27 +1332,27 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>33</v>
+        <v>46121</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>33</v>
+        <v>46121</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -1330,13 +1360,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>33</v>
+        <v>46121</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -1344,13 +1374,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>33</v>
+        <v>46121</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -1358,13 +1388,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>33</v>
+        <v>46121</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -1372,16 +1402,212 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46120</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>42</v>
+        <v>46121</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A170C0-8F85-4741-9C11-D31DE808E5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01804F9B-A4A9-45D9-B2AC-43532AB17C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="169">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,18 +96,9 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Lachlan Olbrich</t>
-  </si>
-  <si>
     <t>CHI</t>
   </si>
   <si>
-    <t>Collin Sexton</t>
-  </si>
-  <si>
-    <t>Patrick Williams</t>
-  </si>
-  <si>
     <t>Isaac Okoro</t>
   </si>
   <si>
@@ -123,27 +114,18 @@
     <t>Anfernee Simons</t>
   </si>
   <si>
-    <t>Justin Champagnie</t>
-  </si>
-  <si>
     <t>WAS</t>
   </si>
   <si>
     <t>Bilal Coulibaly</t>
   </si>
   <si>
-    <t>Anthony Gill</t>
-  </si>
-  <si>
     <t>Jaden Hardy</t>
   </si>
   <si>
     <t>Tre Johnson</t>
   </si>
   <si>
-    <t>Anthony Davis</t>
-  </si>
-  <si>
     <t>Alex Sarr</t>
   </si>
   <si>
@@ -153,9 +135,6 @@
     <t>Trae Young</t>
   </si>
   <si>
-    <t>Norman Powell</t>
-  </si>
-  <si>
     <t>MIA</t>
   </si>
   <si>
@@ -177,9 +156,6 @@
     <t>Ben Sheppard</t>
   </si>
   <si>
-    <t>Jarace Walker</t>
-  </si>
-  <si>
     <t>TJ McConnell</t>
   </si>
   <si>
@@ -213,27 +189,12 @@
     <t>Ziaire Williams</t>
   </si>
   <si>
-    <t>Danny Wolf</t>
-  </si>
-  <si>
-    <t>Michael Porter Jr.</t>
-  </si>
-  <si>
     <t>Jaylen Brown</t>
   </si>
   <si>
     <t>BOS</t>
   </si>
   <si>
-    <t>Sam Hauser</t>
-  </si>
-  <si>
-    <t>Neemias Queta</t>
-  </si>
-  <si>
-    <t>Derrick White</t>
-  </si>
-  <si>
     <t>Tyler Kolek</t>
   </si>
   <si>
@@ -246,9 +207,6 @@
     <t>PHI</t>
   </si>
   <si>
-    <t>Cameron Payne</t>
-  </si>
-  <si>
     <t>Marcus Smart</t>
   </si>
   <si>
@@ -270,9 +228,6 @@
     <t>GSW</t>
   </si>
   <si>
-    <t>Charles Bassey</t>
-  </si>
-  <si>
     <t>Stephen Curry</t>
   </si>
   <si>
@@ -289,6 +244,294 @@
   </si>
   <si>
     <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Jaylon Tyson</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Jarrett Allen</t>
+  </si>
+  <si>
+    <t>Thomas Bryant</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Coby White</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>Saddiq Bey</t>
+  </si>
+  <si>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>Herbert Jones</t>
+  </si>
+  <si>
+    <t>Karlo Matkovic</t>
+  </si>
+  <si>
+    <t>Bryce McGowens</t>
+  </si>
+  <si>
+    <t>Yves Missi</t>
+  </si>
+  <si>
+    <t>Trey Murphy III</t>
+  </si>
+  <si>
+    <t>Dejounte Murray</t>
+  </si>
+  <si>
+    <t>Zion Williamson</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Trayce Jackson-Davis</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Jett Howard</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>Guerschon Yabusele</t>
+  </si>
+  <si>
+    <t>Giannis Antetokounmpo</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Bobby Portis</t>
+  </si>
+  <si>
+    <t>Gary Trent</t>
+  </si>
+  <si>
+    <t>Cooper Flagg</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Daniel Gafford</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Caleb Martin</t>
+  </si>
+  <si>
+    <t>PJ Washington</t>
+  </si>
+  <si>
+    <t>Brandon Williams</t>
+  </si>
+  <si>
+    <t>Stephon Castle</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Victor Wembanyama</t>
+  </si>
+  <si>
+    <t>Alex Caruso</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Shai Gilgeous-Alexander</t>
+  </si>
+  <si>
+    <t>Isaiah Hartenstein</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>Ajay Mitchell</t>
+  </si>
+  <si>
+    <t>Cason Wallace</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>Jaylin Williams</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Nikola Jokic</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
+    <t>Spencer Jones</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Bones Hyland</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Rudy Gobert</t>
+  </si>
+  <si>
+    <t>Joe Ingles</t>
+  </si>
+  <si>
+    <t>Walter Clayton Jr.</t>
+  </si>
+  <si>
+    <t>Javon Small</t>
+  </si>
+  <si>
+    <t>Olivier-Maxence Prosper</t>
+  </si>
+  <si>
+    <t>Cedric Coward</t>
+  </si>
+  <si>
+    <t>Taylor Hendricks</t>
+  </si>
+  <si>
+    <t>GG Jackson</t>
+  </si>
+  <si>
+    <t>Ty Jerome</t>
+  </si>
+  <si>
+    <t>Cam Spencer</t>
+  </si>
+  <si>
+    <t>Elijah Harkless</t>
+  </si>
+  <si>
+    <t>UTA</t>
+  </si>
+  <si>
+    <t>Isaiah Collier</t>
+  </si>
+  <si>
+    <t>Kyle Filipowski</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Lauri Markkanen</t>
+  </si>
+  <si>
+    <t>Brice Sensabaugh</t>
+  </si>
+  <si>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Jerami Grant</t>
+  </si>
+  <si>
+    <t>DeMar DeRozan</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Keegan Murray</t>
+  </si>
+  <si>
+    <t>Russell Westbrook</t>
+  </si>
+  <si>
+    <t>Jalen Green</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Devin Booker</t>
+  </si>
+  <si>
+    <t>Jordan Goodwin</t>
+  </si>
+  <si>
+    <t>Haywood Highsmith</t>
   </si>
 </sst>
 </file>
@@ -802,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -842,69 +1085,69 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -912,13 +1155,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -926,27 +1169,27 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>24</v>
+        <v>46122</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -954,13 +1197,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -968,13 +1211,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -982,13 +1225,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -996,13 +1239,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1010,27 +1253,27 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="7" t="s">
+        <v>46122</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="C14" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -1038,55 +1281,55 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>33</v>
+        <v>46122</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>43</v>
+        <v>46122</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1094,13 +1337,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>43</v>
+        <v>46122</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1108,13 +1351,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>43</v>
+        <v>46122</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -1122,13 +1365,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>43</v>
+        <v>46122</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -1136,83 +1379,83 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -1220,167 +1463,167 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>48</v>
+        <v>46122</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>56</v>
+        <v>46122</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="6" t="s">
+        <v>46122</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>56</v>
       </c>
+      <c r="C37" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>65</v>
+        <v>46122</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>65</v>
+        <v>46122</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>65</v>
+        <v>46122</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -1388,13 +1631,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>65</v>
+        <v>46122</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -1402,13 +1645,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>70</v>
+        <v>46122</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -1416,111 +1659,111 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>72</v>
+        <v>46122</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>72</v>
+        <v>46122</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>75</v>
+        <v>46122</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>75</v>
+        <v>46122</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>75</v>
+        <v>46122</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>75</v>
+        <v>46122</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -1528,13 +1771,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -1542,41 +1785,41 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
@@ -1584,29 +1827,897 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>80</v>
+        <v>46122</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="9">
-        <v>46121</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C56" s="7" t="s">
+        <v>46122</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D90" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D100" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D107" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D112" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D113" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D114" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D117" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" s="9">
+        <v>46122</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D118" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01804F9B-A4A9-45D9-B2AC-43532AB17C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B75AA44-8C2C-43D9-B8D7-B3C60D66DF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="219">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -105,24 +105,12 @@
     <t>Matas Buzelis</t>
   </si>
   <si>
-    <t>Josh Giddey</t>
-  </si>
-  <si>
-    <t>Nick Richards</t>
-  </si>
-  <si>
-    <t>Anfernee Simons</t>
-  </si>
-  <si>
     <t>WAS</t>
   </si>
   <si>
     <t>Bilal Coulibaly</t>
   </si>
   <si>
-    <t>Jaden Hardy</t>
-  </si>
-  <si>
     <t>Tre Johnson</t>
   </si>
   <si>
@@ -207,9 +195,6 @@
     <t>PHI</t>
   </si>
   <si>
-    <t>Marcus Smart</t>
-  </si>
-  <si>
     <t>LAL</t>
   </si>
   <si>
@@ -228,27 +213,12 @@
     <t>GSW</t>
   </si>
   <si>
-    <t>Stephen Curry</t>
-  </si>
-  <si>
-    <t>Gui Santos</t>
-  </si>
-  <si>
     <t>Will Richard</t>
   </si>
   <si>
-    <t>Al Horford</t>
-  </si>
-  <si>
-    <t>Kristaps Porzingis</t>
-  </si>
-  <si>
     <t>Quinten Post</t>
   </si>
   <si>
-    <t>Jaylon Tyson</t>
-  </si>
-  <si>
     <t>CLE</t>
   </si>
   <si>
@@ -273,9 +243,6 @@
     <t>ATL</t>
   </si>
   <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
     <t>DET</t>
   </si>
   <si>
@@ -330,9 +297,6 @@
     <t>Jonathan Isaac</t>
   </si>
   <si>
-    <t>Guerschon Yabusele</t>
-  </si>
-  <si>
     <t>Giannis Antetokounmpo</t>
   </si>
   <si>
@@ -345,9 +309,6 @@
     <t>Gary Trent</t>
   </si>
   <si>
-    <t>Cooper Flagg</t>
-  </si>
-  <si>
     <t>DAL</t>
   </si>
   <si>
@@ -441,9 +402,6 @@
     <t>Rudy Gobert</t>
   </si>
   <si>
-    <t>Joe Ingles</t>
-  </si>
-  <si>
     <t>Walter Clayton Jr.</t>
   </si>
   <si>
@@ -486,9 +444,6 @@
     <t>Lauri Markkanen</t>
   </si>
   <si>
-    <t>Brice Sensabaugh</t>
-  </si>
-  <si>
     <t>Isaiah Jackson</t>
   </si>
   <si>
@@ -501,9 +456,6 @@
     <t>POR</t>
   </si>
   <si>
-    <t>Shaedon Sharpe</t>
-  </si>
-  <si>
     <t>Jerami Grant</t>
   </si>
   <si>
@@ -532,6 +484,204 @@
   </si>
   <si>
     <t>Haywood Highsmith</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Payton Pritchard</t>
+  </si>
+  <si>
+    <t>Nikola Vucevic</t>
+  </si>
+  <si>
+    <t>Neemias Queta</t>
+  </si>
+  <si>
+    <t>Jayson Tatum</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Anthony Gill</t>
+  </si>
+  <si>
+    <t>Anthony Davis</t>
+  </si>
+  <si>
+    <t>Keon Ellis</t>
+  </si>
+  <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Dennis Schroder</t>
+  </si>
+  <si>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Jalen Duren</t>
+  </si>
+  <si>
+    <t>Jarace Walker</t>
+  </si>
+  <si>
+    <t>Nickeil Alexander-Walker</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>Jonathan Kuminga</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Simone Fontecchio</t>
+  </si>
+  <si>
+    <t>Norman Powell</t>
+  </si>
+  <si>
+    <t>OG Anunoby</t>
+  </si>
+  <si>
+    <t>Jalen Brunson</t>
+  </si>
+  <si>
+    <t>Josh Hart</t>
+  </si>
+  <si>
+    <t>Mitchell Robinson</t>
+  </si>
+  <si>
+    <t>Karl-Anthony Towns</t>
+  </si>
+  <si>
+    <t>Gary Harris</t>
+  </si>
+  <si>
+    <t>Pete Nance</t>
+  </si>
+  <si>
+    <t>Kyle Kuzma</t>
+  </si>
+  <si>
+    <t>Ryan Rollins</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Ochai Agbaji</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Lachlan Olbrich</t>
+  </si>
+  <si>
+    <t>Collin Sexton</t>
+  </si>
+  <si>
+    <t>Patrick Williams</t>
+  </si>
+  <si>
+    <t>Marvin Bagley</t>
+  </si>
+  <si>
+    <t>Adama Bal</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>Alperen Sengun</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Jabari Smith Jr.</t>
+  </si>
+  <si>
+    <t>Amen Thompson</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Kawhi Leonard</t>
+  </si>
+  <si>
+    <t>LeBron James</t>
+  </si>
+  <si>
+    <t>Kyle Anderson</t>
+  </si>
+  <si>
+    <t>Mike Conley</t>
+  </si>
+  <si>
+    <t>Jaden McDaniels</t>
+  </si>
+  <si>
+    <t>Naz Reid</t>
+  </si>
+  <si>
+    <t>Malik Monk</t>
+  </si>
+  <si>
+    <t>Isaiah Stevens</t>
+  </si>
+  <si>
+    <t>Matisse Thybulle</t>
+  </si>
+  <si>
+    <t>Christian Braun</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Cameron Johnson</t>
+  </si>
+  <si>
+    <t>Devin Vassell</t>
+  </si>
+  <si>
+    <t>Luke Kornet</t>
+  </si>
+  <si>
+    <t>Collin Gillespie</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Grayson Allen</t>
+  </si>
+  <si>
+    <t>Dillon Brooks</t>
+  </si>
+  <si>
+    <t>Royce O'Neale</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1085,13 +1235,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>74</v>
+        <v>46124</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1099,69 +1249,69 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>74</v>
+        <v>46124</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>74</v>
+        <v>46124</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>74</v>
+        <v>46124</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>74</v>
+        <v>46124</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>81</v>
+        <v>46124</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1169,27 +1319,27 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>36</v>
+        <v>46124</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>36</v>
+        <v>46124</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1197,27 +1347,27 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>29</v>
+        <v>46124</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
+        <v>46124</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1225,55 +1375,55 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>29</v>
+        <v>46124</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>29</v>
+        <v>46124</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>29</v>
+        <v>46124</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="7" t="s">
+        <v>46124</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>29</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -1281,83 +1431,83 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>83</v>
+        <v>46124</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>85</v>
+        <v>46124</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -1365,13 +1515,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -1379,13 +1529,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -1393,13 +1543,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -1407,13 +1557,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>87</v>
+        <v>46124</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -1421,55 +1571,55 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>55</v>
+        <v>46124</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>59</v>
+        <v>46124</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>59</v>
+        <v>46124</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>41</v>
+        <v>46124</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -1477,13 +1627,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>41</v>
+        <v>46124</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -1491,69 +1641,69 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>41</v>
+        <v>46124</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>41</v>
+        <v>46124</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="7" t="s">
+        <v>46124</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>41</v>
       </c>
+      <c r="C33" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>41</v>
+        <v>46124</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>97</v>
+        <v>46124</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -1561,27 +1711,27 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>97</v>
+        <v>46124</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>57</v>
+        <v>46124</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -1589,41 +1739,41 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>99</v>
+        <v>46124</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>99</v>
+        <v>46124</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>23</v>
+        <v>46124</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -1631,41 +1781,41 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>23</v>
+        <v>46124</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>23</v>
+        <v>46124</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>23</v>
+        <v>46124</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -1673,125 +1823,125 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>23</v>
+        <v>46124</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>23</v>
+        <v>46124</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>48</v>
+        <v>46124</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>48</v>
+        <v>46124</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>48</v>
+        <v>46124</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>48</v>
+        <v>46124</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B50" s="6" t="s">
+        <v>46124</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>48</v>
+      <c r="C50" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B51" s="7" t="s">
+        <v>46124</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>103</v>
+        <v>46124</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
@@ -1799,181 +1949,181 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>103</v>
+        <v>46124</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>103</v>
+        <v>46124</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>107</v>
+        <v>46124</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>107</v>
+        <v>46124</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D56" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>107</v>
+        <v>46124</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>107</v>
+        <v>46124</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>107</v>
+        <v>46124</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>107</v>
+        <v>46124</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>114</v>
+        <v>46124</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>114</v>
+        <v>46124</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -1981,13 +2131,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
@@ -1995,13 +2145,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
@@ -2009,13 +2159,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -2023,13 +2173,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -2037,41 +2187,41 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>117</v>
+        <v>46124</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>127</v>
+        <v>46124</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -2079,237 +2229,237 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>127</v>
+        <v>46124</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>127</v>
+        <v>46124</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>127</v>
+        <v>46124</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>127</v>
+        <v>46124</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>133</v>
+        <v>46124</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>133</v>
+        <v>46124</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>133</v>
+        <v>46124</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>133</v>
+        <v>46124</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="D80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>133</v>
+        <v>46124</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>133</v>
+        <v>46124</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="D83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="D84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="D85" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="D89" t="s">
         <v>14</v>
@@ -2317,13 +2467,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>80</v>
+        <v>46124</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D90" t="s">
         <v>14</v>
@@ -2331,27 +2481,27 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>148</v>
+        <v>46124</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>148</v>
+        <v>46124</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D92" t="s">
         <v>14</v>
@@ -2359,13 +2509,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>148</v>
+        <v>46124</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
@@ -2373,13 +2523,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>148</v>
+        <v>46124</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="D94" t="s">
         <v>14</v>
@@ -2387,13 +2537,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>148</v>
+        <v>46124</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="D95" t="s">
         <v>14</v>
@@ -2401,13 +2551,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>148</v>
+        <v>46124</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="D96" t="s">
         <v>14</v>
@@ -2415,13 +2565,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>155</v>
+        <v>46124</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="D97" t="s">
         <v>14</v>
@@ -2429,13 +2579,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>157</v>
+        <v>46124</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
@@ -2443,13 +2593,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>157</v>
+        <v>46124</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -2457,13 +2607,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>157</v>
+        <v>46124</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -2471,27 +2621,27 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="D101" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
@@ -2499,69 +2649,69 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="D103" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D104" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="D105" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D106" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>66</v>
+        <v>46124</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -2569,13 +2719,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>161</v>
+        <v>46124</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D108" t="s">
         <v>14</v>
@@ -2583,55 +2733,55 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>161</v>
+        <v>46124</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>161</v>
+        <v>46124</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>165</v>
+        <v>46124</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D111" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>165</v>
+        <v>46124</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D112" t="s">
         <v>14</v>
@@ -2639,13 +2789,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>165</v>
+        <v>46124</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
@@ -2653,13 +2803,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>165</v>
+        <v>46124</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -2667,41 +2817,41 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>61</v>
+        <v>46124</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="D115" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>61</v>
+        <v>46124</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D116" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>61</v>
+        <v>46124</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="D117" t="s">
         <v>14</v>
@@ -2709,15 +2859,701 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="9">
-        <v>46122</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>61</v>
+        <v>46124</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D118" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A121" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A122" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D122" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A123" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D123" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A124" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A125" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A126" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A127" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D127" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A128" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D128" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A129" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D129" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A131" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D131" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A132" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A134" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D134" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A136" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A137" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D137" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A138" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A139" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A140" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A141" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A142" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A143" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D143" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A144" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A145" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D145" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A146" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A147" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A148" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A149" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D149" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A150" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A151" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A152" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A153" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A154" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A155" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A156" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A157" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D157" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A158" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D158" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A159" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A160" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D160" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A161" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D161" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A162" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D162" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A163" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D163" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A164" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D164" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A165" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D165" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A166" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D166" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A167" s="9">
+        <v>46124</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D167" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FF0B88-0526-409E-8572-7F02D6B7DA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8CFFB5-8BAE-4117-A439-E74D4E9CB493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,28 +96,37 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>Dru Smith</t>
-  </si>
-  <si>
-    <t>Nikola Jovic</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>Jerami Grant</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Grayson Allen</t>
-  </si>
-  <si>
-    <t>Pelle Larsson</t>
+    <t>Jett Howard</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>Trent Watford</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Johni Broome</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>GSW</t>
+  </si>
+  <si>
+    <t>Isaiah Jackson</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -217,9 +226,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,15 +540,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -623,7 +632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -662,72 +671,100 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="9">
-        <v>46126</v>
+      <c r="A2" s="7">
+        <v>46127</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
-        <v>46126</v>
+      <c r="A3" s="7">
+        <v>46127</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="9">
-        <v>46126</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="9">
-        <v>46126</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="9">
-        <v>46126</v>
+      <c r="A6" s="7">
+        <v>46127</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8CFFB5-8BAE-4117-A439-E74D4E9CB493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6794777-3339-4D7A-91B0-AC539E8ADCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,37 +96,52 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Jett Howard</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>Trent Watford</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Johni Broome</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>Quinten Post</t>
-  </si>
-  <si>
-    <t>GSW</t>
-  </si>
-  <si>
-    <t>Isaiah Jackson</t>
-  </si>
-  <si>
-    <t>LAC</t>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Thomas Bryant</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Spencer Jones</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
   </si>
 </sst>
 </file>
@@ -632,7 +647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -672,7 +687,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -686,55 +701,55 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -742,13 +757,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -756,16 +771,44 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
-        <v>46127</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="7">
+        <v>46130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="7">
+        <v>46130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6794777-3339-4D7A-91B0-AC539E8ADCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E4D584-C1F8-4415-B8F1-70DA21D4C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,52 +96,31 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Thomas Bryant</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Spencer Jones</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Kevin Durant</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Grayson Allen</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jordan McLaughlin</t>
+  </si>
+  <si>
+    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -647,7 +626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -687,7 +666,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -696,12 +675,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -710,18 +689,18 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -729,13 +708,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -743,71 +722,15 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
       <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>46130</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="7">
-        <v>46130</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="7">
-        <v>46130</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="7">
-        <v>46130</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E4D584-C1F8-4415-B8F1-70DA21D4C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2C6066-5795-4069-8AB6-66353030CDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,31 +96,43 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Grayson Allen</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Mark Williams</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jordan McLaughlin</t>
-  </si>
-  <si>
-    <t>SAS</t>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Thomas Bryant</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>OG Anunoby</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>DEN</t>
   </si>
 </sst>
 </file>
@@ -626,7 +638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -666,7 +678,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -675,12 +687,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -689,18 +701,18 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -708,21 +720,21 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -731,6 +743,34 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>46132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>46132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2C6066-5795-4069-8AB6-66353030CDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A03C7-6088-4747-B792-361DCEC8EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,43 +96,37 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Thomas Bryant</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>OG Anunoby</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
-  </si>
-  <si>
-    <t>DEN</t>
+    <t>Ron Harper Jr.</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Jordan McLaughlin</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
   </si>
 </sst>
 </file>
@@ -638,7 +632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -678,7 +672,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -687,12 +681,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -706,7 +700,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -715,62 +709,48 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="7">
-        <v>46132</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A03C7-6088-4747-B792-361DCEC8EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8B0170-9BAE-4488-96A0-4451E1B515A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,37 +96,40 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Ron Harper Jr.</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Jordan McLaughlin</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Kevin Durant</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Thomas Bryant</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Ja'Kobe Walter</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
   </si>
 </sst>
 </file>
@@ -632,7 +635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -672,7 +675,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -681,12 +684,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -695,12 +698,12 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -709,18 +712,18 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -728,30 +731,44 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8B0170-9BAE-4488-96A0-4451E1B515A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FCDA36-CEDB-46F6-A497-724CE289311E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,40 +96,31 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Thomas Bryant</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Ja'Kobe Walter</t>
-  </si>
-  <si>
-    <t>Aaron Gordon</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Victor Wembanyama</t>
+  </si>
+  <si>
+    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -635,7 +626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -675,7 +666,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -684,12 +675,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -703,27 +694,27 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -731,7 +722,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
@@ -740,34 +731,6 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>46135</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="7">
-        <v>46135</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FCDA36-CEDB-46F6-A497-724CE289311E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EA0B98-E21D-4464-9F8D-DCE1CA5EFCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,31 +96,46 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Kevin Durant</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>Victor Wembanyama</t>
-  </si>
-  <si>
-    <t>SAS</t>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>Grayson Allen</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Jordan Goodwin</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
   </si>
 </sst>
 </file>
@@ -626,7 +641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -666,7 +681,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -680,7 +695,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -689,12 +704,12 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -708,7 +723,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -722,16 +737,72 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>46137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>46137</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="7">
+        <v>46137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="7">
+        <v>46137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EA0B98-E21D-4464-9F8D-DCE1CA5EFCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A9C17B-CE11-4DD6-A9A7-6C5A9A50430F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,46 +96,46 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Isaiah Joe</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>Grayson Allen</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Jordan Goodwin</t>
-  </si>
-  <si>
-    <t>Mark Williams</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Aaron Gordon</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
+    <t>A.J. Lawson</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Jordan McLaughlin</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Victor Wembanyama</t>
+  </si>
+  <si>
+    <t>Kelly Oubre Jr.</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>HOU</t>
   </si>
 </sst>
 </file>
@@ -681,7 +681,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -690,46 +690,46 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -751,21 +751,21 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
@@ -774,35 +774,35 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A9C17B-CE11-4DD6-A9A7-6C5A9A50430F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3BEE16-117C-4C56-B86A-10CD839EACEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,46 +96,49 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>A.J. Lawson</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Jordan McLaughlin</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Victor Wembanyama</t>
-  </si>
-  <si>
-    <t>Kelly Oubre Jr.</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Kevin Durant</t>
-  </si>
-  <si>
-    <t>HOU</t>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Jordan Goodwin</t>
+  </si>
+  <si>
+    <t>PHX</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
   </si>
 </sst>
 </file>
@@ -681,7 +684,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -695,41 +698,41 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -737,72 +740,72 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3BEE16-117C-4C56-B86A-10CD839EACEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554990B2-526C-4A71-8437-03D3447BA831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,49 +96,16 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Jordan Goodwin</t>
-  </si>
-  <si>
-    <t>PHX</t>
-  </si>
-  <si>
-    <t>Mark Williams</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
-  </si>
-  <si>
-    <t>Aaron Gordon</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
   </si>
 </sst>
 </file>
@@ -644,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -684,7 +651,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -693,12 +660,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -707,104 +674,6 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="7">
-        <v>46139</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554990B2-526C-4A71-8437-03D3447BA831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529695A2-D6BD-48B0-9E34-A09BF84258F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,16 +96,40 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
+    <t>Franz Wagner</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Austin Reaves</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
   </si>
 </sst>
 </file>
@@ -611,7 +635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -651,7 +675,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -660,20 +684,90 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529695A2-D6BD-48B0-9E34-A09BF84258F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7783F1B1-8F9D-48EE-AF88-F080879432B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,40 +96,43 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Franz Wagner</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Kevin Durant</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>Austin Reaves</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
+    <t>Josh Hart</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Peyton Watson</t>
+  </si>
+  <si>
+    <t>Bones Hyland</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Donte DiVincenzo</t>
   </si>
 </sst>
 </file>
@@ -635,7 +638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -675,7 +678,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -689,55 +692,55 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -745,7 +748,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -759,7 +762,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -768,6 +771,20 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7783F1B1-8F9D-48EE-AF88-F080879432B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77380E7D-90C7-447B-9B41-BD658FD178EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,43 +96,43 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Josh Hart</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>Jock Landale</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Aaron Gordon</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>Peyton Watson</t>
-  </si>
-  <si>
-    <t>Bones Hyland</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Donte DiVincenzo</t>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Tobias Harris</t>
+  </si>
+  <si>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Franz Wagner</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Kevin Durant</t>
+  </si>
+  <si>
+    <t>HOU</t>
   </si>
 </sst>
 </file>
@@ -678,13 +678,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -692,80 +692,80 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -776,16 +776,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
         <v>35</v>
       </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77380E7D-90C7-447B-9B41-BD658FD178EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A700DCB-4235-4DED-80F5-23C00E6E2CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,43 +96,10 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Tobias Harris</t>
-  </si>
-  <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Franz Wagner</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Kevin Durant</t>
-  </si>
-  <si>
-    <t>HOU</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
   </si>
 </sst>
 </file>
@@ -638,7 +605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -678,114 +645,16 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="7">
-        <v>46143</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A700DCB-4235-4DED-80F5-23C00E6E2CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BCFD3C-E5FE-4B2C-A977-9E7771B752BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,10 +96,28 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
+    <t>Jonathan Isaac</t>
+  </si>
+  <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>Franz Wagner</t>
+  </si>
+  <si>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Immanuel Quickley</t>
   </si>
 </sst>
 </file>
@@ -605,7 +623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -645,7 +663,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -654,7 +672,63 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="7">
+        <v>46145</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>46145</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>46145</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="7">
+        <v>46145</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BCFD3C-E5FE-4B2C-A977-9E7771B752BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF66C9-6972-4023-9F65-7902FAE33568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,28 +96,34 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Jonathan Isaac</t>
-  </si>
-  <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>Franz Wagner</t>
-  </si>
-  <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Brandon Ingram</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>Immanuel Quickley</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Jeremy Sochan</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Donte Divincenzo</t>
+  </si>
+  <si>
+    <t>Carter Bryant</t>
+  </si>
+  <si>
+    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -623,7 +629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -663,7 +669,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -672,32 +678,32 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -705,13 +711,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -719,16 +725,30 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>46146</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF66C9-6972-4023-9F65-7902FAE33568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA84425-300E-4951-978C-C65520FD7534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,34 +96,22 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Jeremy Sochan</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Donte Divincenzo</t>
-  </si>
-  <si>
-    <t>Carter Bryant</t>
-  </si>
-  <si>
-    <t>SAS</t>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
   </si>
 </sst>
 </file>
@@ -629,7 +617,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -669,7 +657,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -678,12 +666,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -692,12 +680,12 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -706,49 +694,7 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
-        <v>46146</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="7">
-        <v>46146</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>46146</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA84425-300E-4951-978C-C65520FD7534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F597A1-5631-41CC-A347-2CCE7A87A504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,22 +96,25 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Carter Bryant</t>
+  </si>
+  <si>
+    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -617,7 +620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -657,7 +660,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -666,12 +669,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -680,21 +683,35 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F597A1-5631-41CC-A347-2CCE7A87A504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67633E83-3589-49B1-AD2D-F602643EE8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,25 +96,31 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
-  </si>
-  <si>
-    <t>Carter Bryant</t>
-  </si>
-  <si>
-    <t>SAS</t>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Luke Kennard</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Jarred Vanderbilt</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
   </si>
 </sst>
 </file>
@@ -620,7 +626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -660,7 +666,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -669,12 +675,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -683,18 +689,18 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -702,16 +708,44 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="7">
+        <v>46149</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>46149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67633E83-3589-49B1-AD2D-F602643EE8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6EF2B6-6627-48DE-A9C8-51478E5DA27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,31 +96,31 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Luke Kennard</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Jarred Vanderbilt</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
+    <t>Mitchell Robinson</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>OG Anunoby</t>
+  </si>
+  <si>
+    <t>Josh Hart</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Ayo Dosunmu</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
   </si>
 </sst>
 </file>
@@ -666,7 +666,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -675,32 +675,32 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -708,44 +708,44 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6EF2B6-6627-48DE-A9C8-51478E5DA27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC62E4E-1B8E-45F5-B322-BA52E38697D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,31 +96,31 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Mitchell Robinson</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>OG Anunoby</t>
-  </si>
-  <si>
-    <t>Josh Hart</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Ayo Dosunmu</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Anthony Edwards</t>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Sam Merrill</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Jarred Vanderbilt</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
   </si>
 </sst>
 </file>
@@ -626,7 +626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -675,18 +675,18 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -694,27 +694,27 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -722,30 +722,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>46150</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC62E4E-1B8E-45F5-B322-BA52E38697D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ABDB48-3180-4BE1-B60F-A6DA31838760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,31 +96,16 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Sam Merrill</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Jarred Vanderbilt</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
+    <t>OG Anunoby</t>
+  </si>
+  <si>
+    <t>NYK</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>PHI</t>
   </si>
 </sst>
 </file>
@@ -626,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -666,7 +651,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -675,12 +660,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -689,49 +674,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
-        <v>46151</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
-        <v>46151</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="7">
-        <v>46151</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ABDB48-3180-4BE1-B60F-A6DA31838760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65BFBB1-F816-4EE7-8C69-EECC25CE1FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,16 +96,25 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>OG Anunoby</t>
-  </si>
-  <si>
-    <t>NYK</t>
-  </si>
-  <si>
-    <t>Joel Embiid</t>
-  </si>
-  <si>
-    <t>PHI</t>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Caris LeVert</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>LAL</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -651,7 +660,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -665,16 +674,44 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>46153</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>46153</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65BFBB1-F816-4EE7-8C69-EECC25CE1FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B683E4D0-0271-4A9E-84CF-94741B373C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,25 +96,10 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Caris LeVert</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Luka Doncic</t>
-  </si>
-  <si>
-    <t>LAL</t>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -620,7 +605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -660,7 +645,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -670,48 +655,6 @@
       </c>
       <c r="D2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
-        <v>46153</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
-        <v>46153</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
-        <v>46153</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B683E4D0-0271-4A9E-84CF-94741B373C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E5E810-3F7B-49C8-AEBB-32DED9295212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,10 +96,16 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>De'Aaron Fox</t>
-  </si>
-  <si>
-    <t>SAS</t>
+    <t>Kevin Huerter</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Caris LeVert</t>
+  </si>
+  <si>
+    <t>Duncan Robinson</t>
   </si>
 </sst>
 </file>
@@ -605,7 +611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -645,7 +651,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -654,6 +660,34 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E5E810-3F7B-49C8-AEBB-32DED9295212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74BB560-95AA-4DCB-AAF3-E8CA77F43B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -651,7 +651,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74BB560-95AA-4DCB-AAF3-E8CA77F43B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16042CEF-BAC0-46C1-9F64-1D4397F9A9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -651,7 +651,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16042CEF-BAC0-46C1-9F64-1D4397F9A9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38119ED-180B-4A39-9A66-CF9FC48D0505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,16 +96,10 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Kevin Huerter</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Caris LeVert</t>
-  </si>
-  <si>
-    <t>Duncan Robinson</t>
+    <t>OG Anunoby</t>
+  </si>
+  <si>
+    <t>NYK</t>
   </si>
 </sst>
 </file>
@@ -611,7 +605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -651,7 +645,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -660,35 +654,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
-        <v>46159</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
-        <v>46159</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38119ED-180B-4A39-9A66-CF9FC48D0505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1AA1CB-D001-49A0-8F9D-092525ED9C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,10 +96,10 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>OG Anunoby</t>
-  </si>
-  <si>
-    <t>NYK</t>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -645,7 +645,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -654,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1AA1CB-D001-49A0-8F9D-092525ED9C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A678FD2-8204-4A32-AE56-22F18C055153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,12 +94,6 @@
   </si>
   <si>
     <t>Quick rules</t>
-  </si>
-  <si>
-    <t>De'Aaron Fox</t>
-  </si>
-  <si>
-    <t>SAS</t>
   </si>
 </sst>
 </file>
@@ -189,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -199,7 +193,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -513,15 +506,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -605,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -643,20 +636,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="7">
-        <v>46162</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A678FD2-8204-4A32-AE56-22F18C055153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5656F1-7F69-4E9D-A742-F9FEE09C6797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,6 +94,21 @@
   </si>
   <si>
     <t>Quick rules</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>SAS</t>
+  </si>
+  <si>
+    <t>Dylan Harper</t>
   </si>
 </sst>
 </file>
@@ -183,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -195,6 +210,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,7 +614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -636,6 +652,48 @@
         <v>22</v>
       </c>
     </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9">
+        <v>46164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="9">
+        <v>46164</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="9">
+        <v>46164</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5656F1-7F69-4E9D-A742-F9FEE09C6797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95D6FFD-AA05-4DEE-8519-56A07ADA2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,21 +94,6 @@
   </si>
   <si>
     <t>Quick rules</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>De'Aaron Fox</t>
-  </si>
-  <si>
-    <t>SAS</t>
-  </si>
-  <si>
-    <t>Dylan Harper</t>
   </si>
 </sst>
 </file>
@@ -198,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -210,7 +195,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -652,48 +636,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="9">
-        <v>46164</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
-        <v>46164</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="9">
-        <v>46164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95D6FFD-AA05-4DEE-8519-56A07ADA2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99B6E4B-4BB4-4BB5-84A4-A608CB7AD57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,6 +94,15 @@
   </si>
   <si>
     <t>Quick rules</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Ajay Mitchell</t>
   </si>
 </sst>
 </file>
@@ -183,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -195,6 +204,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -636,6 +646,34 @@
         <v>22</v>
       </c>
     </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9">
+        <v>46166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="9">
+        <v>46166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99B6E4B-4BB4-4BB5-84A4-A608CB7AD57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A567A0-27C0-4068-89D0-C97C1631D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,15 +94,6 @@
   </si>
   <si>
     <t>Quick rules</t>
-  </si>
-  <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Ajay Mitchell</t>
   </si>
 </sst>
 </file>
@@ -192,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -204,7 +195,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -646,34 +636,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="9">
-        <v>46166</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
-        <v>46166</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A567A0-27C0-4068-89D0-C97C1631D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F883111A-D1D0-49E0-A5A8-CA28D30F896F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,6 +94,15 @@
   </si>
   <si>
     <t>Quick rules</t>
+  </si>
+  <si>
+    <t>Jalen Williams</t>
+  </si>
+  <si>
+    <t>OKC</t>
+  </si>
+  <si>
+    <t>Ajay Mitchell</t>
   </si>
 </sst>
 </file>
@@ -183,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -195,6 +204,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -636,6 +646,34 @@
         <v>22</v>
       </c>
     </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F883111A-D1D0-49E0-A5A8-CA28D30F896F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C72BD73-11F8-4703-8722-3D25F89DDC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,9 +202,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,15 +516,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -647,8 +647,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="9">
-        <v>46168</v>
+      <c r="A2" s="7">
+        <v>46170</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -661,8 +661,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
-        <v>46168</v>
+      <c r="A3" s="7">
+        <v>46170</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C72BD73-11F8-4703-8722-3D25F89DDC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387C4697-E0E7-454D-8EE9-9C77ABA17214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -648,7 +648,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -657,12 +657,12 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387C4697-E0E7-454D-8EE9-9C77ABA17214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D273D8FD-5B1F-41B4-840B-853246189C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -96,13 +96,10 @@
     <t>Quick rules</t>
   </si>
   <si>
-    <t>Jalen Williams</t>
-  </si>
-  <si>
-    <t>OKC</t>
-  </si>
-  <si>
-    <t>Ajay Mitchell</t>
+    <t>Mitchell Robinson</t>
+  </si>
+  <si>
+    <t>NYK</t>
   </si>
 </sst>
 </file>
@@ -608,7 +605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -648,7 +645,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -657,21 +654,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
-        <v>46172</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D273D8FD-5B1F-41B4-840B-853246189C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4182960C-A429-41E6-BE41-8151A22A4648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -645,7 +645,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>

--- a/data/nba_injuries.xlsx
+++ b/data/nba_injuries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\letsparlayml.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4182960C-A429-41E6-BE41-8151A22A4648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B373F9FA-2173-4940-995E-19D9CC1DEF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>NBA Injury Context Template</t>
   </si>
@@ -94,12 +94,6 @@
   </si>
   <si>
     <t>Quick rules</t>
-  </si>
-  <si>
-    <t>Mitchell Robinson</t>
-  </si>
-  <si>
-    <t>NYK</t>
   </si>
 </sst>
 </file>
@@ -189,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -199,7 +193,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -513,15 +506,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.65">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -605,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -643,20 +636,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="7">
-        <v>46178</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
